--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,27 +397,966 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q17"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
     <col min="12" max="12" width="22.83203125" customWidth="1"/>
     <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="30.83203125" customWidth="1"/>
-    <col min="15" max="15" width="25.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="30.83203125" customWidth="1"/>
+    <col min="16" max="16" width="25.83203125" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>S.No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Candidate Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>WhatsApp Phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Role Applied</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Work Mode</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Interview Mode</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Portfolio / Drive / Social Link</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Candidate Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Interview Date &amp; Time</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Experience</v>
+      </c>
+      <c r="L1" t="str">
+        <v>City</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Resume Reminder Sent</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Interview 1hr Reminder</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Applied Date</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Last Message</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C2" t="str">
+        <v>+919876543211</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="F2" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Social: @tech_creator (45k)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Preferred: Influencer Collaboration</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M2" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N2" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O2" t="str">
+        <v>14-Sept-2026, 2:30 pm</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Hello, I want to connect for Influencer Collaboration. My instagram is @tech_creator with 45k followers</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C3" t="str">
+        <v>+919876543210</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="F3" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G3" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Preferred: Freelancer</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M3" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N3" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O3" t="str">
+        <v>14-Sept-2026, 2:30 pm</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Hi I am Rahul, I want to apply for video editor freelance work from home</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+918357977322</v>
+      </c>
+      <c r="D4" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F4" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J4" t="str">
+        <v>08-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O4" t="str">
+        <v>07-Sept-2026, 1:26 pm</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Great! See you at the interview. 👍 All the best! 😊</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Tanmay Jain</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+919993297342</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Digital Marketing Manager</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F5" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G5" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K5" t="str">
+        <v>6 years</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O5" t="str">
+        <v>07-Sept-2026, 11:48 am</v>
+      </c>
+      <c r="P5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Tanmay Jain! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Shyama's house of snacks</v>
+      </c>
+      <c r="C6" t="str">
+        <v>+917693884339</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Digital Marketing Manager</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F6" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G6" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J6" t="str">
+        <v>05-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O6" t="str">
+        <v>04-Sept-2026, 2:28 pm</v>
+      </c>
+      <c r="P6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Shyama's house of snacks! 🔄
+Your interview for the *Digital Marketing Manager* position at *BrandSetu Digital* has been *rescheduled successfully*.
+📅 *Updated Date &amp; Time:* Sat, 5 Sept, 2026, 11:00 am
+📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
+📌 Please bring your updated Resume and work samples/portfolio.
+For any questions or directions, reply here or contact us at +91 9329232025.
+See you then! 👍
+- HR Team, BrandSetu Digital</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>BrandSetuDigital</v>
+      </c>
+      <c r="C7" t="str">
+        <v>+919669765911</v>
+      </c>
+      <c r="D7" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F7" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G7" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N7" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O7" t="str">
+        <v>04-Sept-2026, 2:33 pm</v>
+      </c>
+      <c r="P7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Namaste BrandSetuDigital! 👋
+BrandSetu Digital me *General Applicant* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
+👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Mohit 🎬</v>
+      </c>
+      <c r="C8" t="str">
+        <v>+917470584339</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F8" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N8" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O8" t="str">
+        <v>20-Aug-2026, 4:31 pm</v>
+      </c>
+      <c r="P8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Mohit! 😊
+Aapki profile aur portfolio HR team dwara shortlist kar li gayi hai. 👏✨
+👉 Kya aap kal morning me *10:00 AM se 12:00 PM* ke beech hamare Indore office (*103 Orange Business Park, Bhawarkua*) in-person interview ke liye aa sakte hain? 🏢
+Kripya confirm karein (Haan / Nahi ya apna suitable time batayein). 👍</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>manshi</v>
+      </c>
+      <c r="C9" t="str">
+        <v>+917828966773</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Digital Marketing Manager</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F9" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G9" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O9" t="str">
+        <v>04-Sept-2026, 2:27 pm</v>
+      </c>
+      <c r="P9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Namaste manshi! 👋
+BrandSetu Digital me *Digital Marketing Manager* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
+👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Aabid</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+917869724727</v>
+      </c>
+      <c r="D10" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F10" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J10" t="str">
+        <v>04-Sept-2026, 2:00 pm</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O10" t="str">
+        <v>04-Sept-2026, 2:15 pm</v>
+      </c>
+      <c r="P10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Aabid! 🎉
+Your interview for the *AI Video Expert* position at *BrandSetu Digital* has been scheduled successfully.
+📅 *Date &amp; Time:* Fri, 4 Sept, 2026, 02:00 pm
+📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
+📌 Please bring your updated Resume and work samples/portfolio.
+For any questions or directions, reply here or contact us at +91 9329232025.
+Best of luck! 👍
+- HR Team, BrandSetu Digital</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Nancy Ajmera</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+38899686625461</v>
+      </c>
+      <c r="D11" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F11" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O11" t="str">
+        <v>03-Sept-2026, 5:03 pm</v>
+      </c>
+      <c r="P11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Nancy! 😊
+Welcome to Brand Setu Digital! 🎉
+We are actively hiring for:
+1️⃣ 🎬 *Video Editor*
+2️⃣ 🤖 *AI Video Expert*
+3️⃣ 🎨 *Graphic Designer*
+4️⃣ 🔎 *SEO &amp; AEO Expert*
+5️⃣ 📱 *Social Media Manager*
+6️⃣ 📢 *Digital Marketing Manager*
+👉 Which **position/role** would you like to apply for? (Please reply with number 1 to 6 or the role name) 📝</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Unnat</v>
+      </c>
+      <c r="C12" t="str">
+        <v>+278880866857060</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F12" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H12" t="str">
+        <v>https://corrra.com/@unnatportfolio</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J12" t="str">
+        <v>04-Sept-2026, 4:00 pm</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O12" t="str">
+        <v>03-Sept-2026, 3:58 pm</v>
+      </c>
+      <c r="P12" t="str">
+        <v>4 sep friday</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C13" t="str">
+        <v>+919329232025</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F13" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H13" t="str">
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J13" t="str">
+        <v>04-Sept-2026, 2:00 pm</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O13" t="str">
+        <v>03-Sept-2026, 3:35 pm</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Kal dopahar 2 baje</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Test auto schedule</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C14" t="str">
+        <v>+114405211672638</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F14" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G14" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J14" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N14" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O14" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="P14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Arjun! 😊
+Your interview is already confirmed for *Thu, 3 Sept, 05:00 pm* at 103 Orange Business Park, Bhawarkua, Indore. We look forward to meeting you! 😊📍</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C15" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F15" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G15" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M15" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N15" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O15" t="str">
+        <v>20-Aug-2026, 3:49 pm</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Hello manisha! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Annushka</v>
+      </c>
+      <c r="C16" t="str">
+        <v>+919039193109</v>
+      </c>
+      <c r="D16" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F16" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G16" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M16" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N16" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O16" t="str">
+        <v>10-Sept-2026, 12:45 pm</v>
+      </c>
+      <c r="P16" t="str">
+        <v>Hiiii</v>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>सौमित्र</v>
+      </c>
+      <c r="C17" t="str">
+        <v>+919770477701</v>
+      </c>
+      <c r="D17" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F17" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G17" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Not Interested</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M17" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N17" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O17" t="str">
+        <v>12-Sept-2026, 2:49 pm</v>
+      </c>
+      <c r="P17" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -475,34 +475,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Candidate</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C2" t="str">
-        <v>+919876543211</v>
+        <v>+918357977322</v>
       </c>
       <c r="D2" t="str">
-        <v>Influencer Collaboration</v>
+        <v>SEO &amp; AEO Expert</v>
       </c>
       <c r="E2" t="str">
-        <v>Influencer Collaboration</v>
+        <v>Full-Time</v>
       </c>
       <c r="F2" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="G2" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="H2" t="str">
-        <v>Social: @tech_creator (45k)</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="J2" t="str">
-        <v>Not Scheduled</v>
+        <v>08-Sept-2026, 11:00 am</v>
       </c>
       <c r="K2" t="str">
-        <v>Preferred: Influencer Collaboration</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="L2" t="str">
         <v>Indore</v>
@@ -514,48 +514,48 @@
         <v>NO</v>
       </c>
       <c r="O2" t="str">
-        <v>14-Sept-2026, 2:30 pm</v>
+        <v>07-Sept-2026, 1:26 pm</v>
       </c>
       <c r="P2" t="str">
-        <v>Hello, I want to connect for Influencer Collaboration. My instagram is @tech_creator with 45k followers</v>
+        <v>Great! See you at the interview. 👍 All the best! 😊</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Candidate</v>
+        <v>Tanmay Jain</v>
       </c>
       <c r="C3" t="str">
-        <v>+919876543210</v>
+        <v>+919993297342</v>
       </c>
       <c r="D3" t="str">
-        <v>Video Editor</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E3" t="str">
-        <v>Freelancer</v>
+        <v>Full-Time</v>
       </c>
       <c r="F3" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="G3" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>Applied</v>
+        <v>Resume Received</v>
       </c>
       <c r="J3" t="str">
         <v>Not Scheduled</v>
       </c>
       <c r="K3" t="str">
-        <v>Preferred: Freelancer</v>
+        <v>6 years</v>
       </c>
       <c r="L3" t="str">
         <v>Indore</v>
@@ -567,171 +567,65 @@
         <v>NO</v>
       </c>
       <c r="O3" t="str">
-        <v>14-Sept-2026, 2:30 pm</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Hi I am Rahul, I want to apply for video editor freelance work from home</v>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Arjun Meena</v>
-      </c>
-      <c r="C4" t="str">
-        <v>+918357977322</v>
-      </c>
-      <c r="D4" t="str">
-        <v>SEO &amp; AEO Expert</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F4" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="J4" t="str">
-        <v>08-Sept-2026, 11:00 am</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Experienced (Full-Time)</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O4" t="str">
-        <v>07-Sept-2026, 1:26 pm</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Great! See you at the interview. 👍 All the best! 😊</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Tanmay Jain</v>
-      </c>
-      <c r="C5" t="str">
-        <v>+919993297342</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Digital Marketing Manager</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F5" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G5" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Resume Received</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K5" t="str">
-        <v>6 years</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O5" t="str">
         <v>07-Sept-2026, 11:48 am</v>
       </c>
-      <c r="P5" t="str" xml:space="preserve">
+      <c r="P3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Tanmay Jain! 😊
 Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
 👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
 Please confirm (Yes / No or share your preferred time). 👍</v>
       </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
         <v>Shyama's house of snacks</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C4" t="str">
         <v>+917693884339</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D4" t="str">
         <v>Digital Marketing Manager</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E4" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F6" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G6" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
+      <c r="F4" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J4" t="str">
         <v>05-Sept-2026, 11:00 am</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K4" t="str">
         <v>Fresher (Paid Internship)</v>
       </c>
-      <c r="L6" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O6" t="str">
+      <c r="L4" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O4" t="str">
         <v>04-Sept-2026, 2:28 pm</v>
       </c>
-      <c r="P6" t="str" xml:space="preserve">
+      <c r="P4" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Shyama's house of snacks! 🔄
 Your interview for the *Digital Marketing Manager* position at *BrandSetu Digital* has been *rescheduled successfully*.
 📅 *Updated Date &amp; Time:* Sat, 5 Sept, 2026, 11:00 am
@@ -741,225 +635,225 @@
 See you then! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="Q4" t="str">
         <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
         <v>BrandSetuDigital</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C5" t="str">
         <v>+919669765911</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D5" t="str">
         <v>General Applicant</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E5" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F7" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="F5" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G5" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J5" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M7" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N7" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O7" t="str">
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M5" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O5" t="str">
         <v>04-Sept-2026, 2:33 pm</v>
       </c>
-      <c r="P7" t="str" xml:space="preserve">
+      <c r="P5" t="str" xml:space="preserve">
         <v xml:space="preserve">Namaste BrandSetuDigital! 👋
 BrandSetu Digital me *General Applicant* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
 👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>Mohit 🎬</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C6" t="str">
         <v>+917470584339</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D6" t="str">
         <v>Video Editor</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E6" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F8" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G8" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
+      <c r="F6" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G6" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>Resume Received</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J6" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M8" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N8" t="str">
-        <v>YES</v>
-      </c>
-      <c r="O8" t="str">
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N6" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O6" t="str">
         <v>20-Aug-2026, 4:31 pm</v>
       </c>
-      <c r="P8" t="str" xml:space="preserve">
+      <c r="P6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Mohit! 😊
 Aapki profile aur portfolio HR team dwara shortlist kar li gayi hai. 👏✨
 👉 Kya aap kal morning me *10:00 AM se 12:00 PM* ke beech hamare Indore office (*103 Orange Business Park, Bhawarkua*) in-person interview ke liye aa sakte hain? 🏢
 Kripya confirm karein (Haan / Nahi ya apna suitable time batayein). 👍</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q6" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
         <v>manshi</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C7" t="str">
         <v>+917828966773</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D7" t="str">
         <v>Digital Marketing Manager</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E7" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F9" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="F7" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G7" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J7" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M9" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N9" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O9" t="str">
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N7" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O7" t="str">
         <v>04-Sept-2026, 2:27 pm</v>
       </c>
-      <c r="P9" t="str" xml:space="preserve">
+      <c r="P7" t="str" xml:space="preserve">
         <v xml:space="preserve">Namaste manshi! 👋
 BrandSetu Digital me *Digital Marketing Manager* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
 👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
         <v>Aabid</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C8" t="str">
         <v>+917869724727</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D8" t="str">
         <v>AI Video Expert</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E8" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F10" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G10" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
+      <c r="F8" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J8" t="str">
         <v>04-Sept-2026, 2:00 pm</v>
       </c>
-      <c r="K10" t="str">
+      <c r="K8" t="str">
         <v>Experienced (Full-Time)</v>
       </c>
-      <c r="L10" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O10" t="str">
+      <c r="L8" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O8" t="str">
         <v>04-Sept-2026, 2:15 pm</v>
       </c>
-      <c r="P10" t="str" xml:space="preserve">
+      <c r="P8" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Aabid! 🎉
 Your interview for the *AI Video Expert* position at *BrandSetu Digital* has been scheduled successfully.
 📅 *Date &amp; Time:* Fri, 4 Sept, 2026, 02:00 pm
@@ -969,57 +863,57 @@
 Best of luck! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="Q8" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
         <v>Nancy Ajmera</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C9" t="str">
         <v>+38899686625461</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D9" t="str">
         <v>General Applicant</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E9" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F11" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="F9" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G9" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>Applied</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J9" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M11" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N11" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O11" t="str">
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O9" t="str">
         <v>03-Sept-2026, 5:03 pm</v>
       </c>
-      <c r="P11" t="str" xml:space="preserve">
+      <c r="P9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Nancy! 😊
 Welcome to Brand Setu Digital! 🎉
 We are actively hiring for:
@@ -1031,19 +925,125 @@
 6️⃣ 📢 *Digital Marketing Manager*
 👉 Which **position/role** would you like to apply for? (Please reply with number 1 to 6 or the role name) 📝</v>
       </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Unnat</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+278880866857060</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F10" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H10" t="str">
+        <v>https://corrra.com/@unnatportfolio</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J10" t="str">
+        <v>04-Sept-2026, 4:00 pm</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O10" t="str">
+        <v>03-Sept-2026, 3:58 pm</v>
+      </c>
+      <c r="P10" t="str">
+        <v>4 sep friday</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+919329232025</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F11" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H11" t="str">
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J11" t="str">
+        <v>04-Sept-2026, 2:00 pm</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O11" t="str">
+        <v>03-Sept-2026, 3:35 pm</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Kal dopahar 2 baje</v>
+      </c>
       <c r="Q11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
+        <v>Test auto schedule</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Unnat</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C12" t="str">
-        <v>+278880866857060</v>
+        <v>+114405211672638</v>
       </c>
       <c r="D12" t="str">
         <v>Video Editor</v>
@@ -1058,16 +1058,16 @@
         <v>YES</v>
       </c>
       <c r="H12" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J12" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
+        <v>03-Sept-2026, 5:00 pm</v>
       </c>
       <c r="K12" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="L12" t="str">
         <v>Indore</v>
@@ -1079,13 +1079,14 @@
         <v>YES</v>
       </c>
       <c r="O12" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
-      </c>
-      <c r="P12" t="str">
-        <v>4 sep friday</v>
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="P12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Arjun! 😊
+Your interview is already confirmed for *Thu, 3 Sept, 05:00 pm* at 103 Orange Business Park, Bhawarkua, Indore. We look forward to meeting you! 😊📍</v>
       </c>
       <c r="Q12" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
       </c>
     </row>
     <row r="13">
@@ -1093,10 +1094,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Arjun Meena</v>
+        <v>manisha</v>
       </c>
       <c r="C13" t="str">
-        <v>+919329232025</v>
+        <v>+917879010084</v>
       </c>
       <c r="D13" t="str">
         <v>Video Editor</v>
@@ -1108,51 +1109,51 @@
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="G13" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="H13" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Pending</v>
       </c>
       <c r="J13" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="K13" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v/>
       </c>
       <c r="L13" t="str">
         <v>Indore</v>
       </c>
       <c r="M13" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N13" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="O13" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
+        <v>20-Aug-2026, 3:49 pm</v>
       </c>
       <c r="P13" t="str">
-        <v>Kal dopahar 2 baje</v>
+        <v>Hello manisha! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
       </c>
       <c r="Q13" t="str">
-        <v>Test auto schedule</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Arjun Meena</v>
+        <v>Annushka</v>
       </c>
       <c r="C14" t="str">
-        <v>+114405211672638</v>
+        <v>+919039193109</v>
       </c>
       <c r="D14" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E14" t="str">
         <v>Full-Time</v>
@@ -1161,38 +1162,37 @@
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="G14" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Pending</v>
       </c>
       <c r="J14" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="K14" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v/>
       </c>
       <c r="L14" t="str">
         <v>Indore</v>
       </c>
       <c r="M14" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N14" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="O14" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
-      </c>
-      <c r="P14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Arjun! 😊
-Your interview is already confirmed for *Thu, 3 Sept, 05:00 pm* at 103 Orange Business Park, Bhawarkua, Indore. We look forward to meeting you! 😊📍</v>
+        <v>10-Sept-2026, 12:45 pm</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Hiiii</v>
       </c>
       <c r="Q14" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>manisha</v>
+        <v>सौमित्र</v>
       </c>
       <c r="C15" t="str">
-        <v>+917879010084</v>
+        <v>+919770477701</v>
       </c>
       <c r="D15" t="str">
-        <v>Video Editor</v>
+        <v>AI Video Expert</v>
       </c>
       <c r="E15" t="str">
         <v>Full-Time</v>
@@ -1221,7 +1221,7 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>Resume Pending</v>
+        <v>Not Interested</v>
       </c>
       <c r="J15" t="str">
         <v>Not Scheduled</v>
@@ -1236,13 +1236,13 @@
         <v>YES</v>
       </c>
       <c r="N15" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="O15" t="str">
-        <v>20-Aug-2026, 3:49 pm</v>
+        <v>12-Sept-2026, 2:49 pm</v>
       </c>
       <c r="P15" t="str">
-        <v>Hello manisha! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
+        <v>Hi</v>
       </c>
       <c r="Q15" t="str">
         <v/>
@@ -1253,16 +1253,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Annushka</v>
+        <v>Candidate</v>
       </c>
       <c r="C16" t="str">
-        <v>+919039193109</v>
+        <v>+919876543211</v>
       </c>
       <c r="D16" t="str">
-        <v>General Applicant</v>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="E16" t="str">
-        <v>Full-Time</v>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="F16" t="str">
         <v>In-Person (Indore Office)</v>
@@ -1271,31 +1271,31 @@
         <v>PENDING</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Social: @tech_creator (45k)</v>
       </c>
       <c r="I16" t="str">
-        <v>Resume Pending</v>
+        <v>Applied</v>
       </c>
       <c r="J16" t="str">
         <v>Not Scheduled</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>Preferred: Influencer Collaboration</v>
       </c>
       <c r="L16" t="str">
         <v>Indore</v>
       </c>
       <c r="M16" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N16" t="str">
         <v>NO</v>
       </c>
       <c r="O16" t="str">
-        <v>10-Sept-2026, 12:45 pm</v>
+        <v>14-Sept-2026, 2:30 pm</v>
       </c>
       <c r="P16" t="str">
-        <v>Hiiii</v>
+        <v>Hello, I want to connect for Influencer Collaboration. My instagram is @tech_creator with 45k followers</v>
       </c>
       <c r="Q16" t="str">
         <v/>
@@ -1306,16 +1306,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>सौमित्र</v>
+        <v>Candidate</v>
       </c>
       <c r="C17" t="str">
-        <v>+919770477701</v>
+        <v>+919876543210</v>
       </c>
       <c r="D17" t="str">
-        <v>AI Video Expert</v>
+        <v>Video Editor</v>
       </c>
       <c r="E17" t="str">
-        <v>Full-Time</v>
+        <v>Freelancer</v>
       </c>
       <c r="F17" t="str">
         <v>In-Person (Indore Office)</v>
@@ -1327,28 +1327,28 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>Not Interested</v>
+        <v>Applied</v>
       </c>
       <c r="J17" t="str">
         <v>Not Scheduled</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>Preferred: Freelancer</v>
       </c>
       <c r="L17" t="str">
         <v>Indore</v>
       </c>
       <c r="M17" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N17" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="O17" t="str">
-        <v>12-Sept-2026, 2:49 pm</v>
+        <v>14-Sept-2026, 2:30 pm</v>
       </c>
       <c r="P17" t="str">
-        <v>Hi</v>
+        <v>Hi I am Rahul, I want to apply for video editor freelance work from home</v>
       </c>
       <c r="Q17" t="str">
         <v/>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q52"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -475,19 +475,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Arjun Meena</v>
+        <v>Garima Namdev</v>
       </c>
       <c r="C2" t="str">
-        <v>+918357977322</v>
+        <v>+919713100248</v>
       </c>
       <c r="D2" t="str">
-        <v>SEO &amp; AEO Expert</v>
+        <v>Social Media Manager</v>
       </c>
       <c r="E2" t="str">
-        <v>Full-Time</v>
+        <v>Freelancer</v>
       </c>
       <c r="F2" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v>Online (Google Meet)</v>
       </c>
       <c r="G2" t="str">
         <v>YES</v>
@@ -496,13 +496,13 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Received</v>
       </c>
       <c r="J2" t="str">
-        <v>08-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="K2" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>Experienced [Freelancer]</v>
       </c>
       <c r="L2" t="str">
         <v>Indore</v>
@@ -514,48 +514,48 @@
         <v>NO</v>
       </c>
       <c r="O2" t="str">
-        <v>07-Sept-2026, 1:26 pm</v>
+        <v>16-Sept-2026, 12:04 pm</v>
       </c>
       <c r="P2" t="str">
-        <v>Great! See you at the interview. 👍 All the best! 😊</v>
+        <v>https://garimanamdevportfolio.my.canva.site/creative-portfolio GarimaNamdevResume.pdf</v>
       </c>
       <c r="Q2" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Tanmay Jain</v>
+        <v>Karishma Jaiswani</v>
       </c>
       <c r="C3" t="str">
-        <v>+919993297342</v>
+        <v>+918959264686</v>
       </c>
       <c r="D3" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>Social Media Manager &amp; Content Writer</v>
       </c>
       <c r="E3" t="str">
-        <v>Full-Time</v>
+        <v>Work From Home</v>
       </c>
       <c r="F3" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v>Online (Google Meet)</v>
       </c>
       <c r="G3" t="str">
         <v>YES</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>https://drive.google.com/file/d/1SGpoKwfEDMCdq2VH6pAPQgF7u1Xf_nmh/view?usp=drivesdk</v>
       </c>
       <c r="I3" t="str">
-        <v>Resume Received</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="J3" t="str">
-        <v>Not Scheduled</v>
+        <v>16-Sept-2026, 11:00 am</v>
       </c>
       <c r="K3" t="str">
-        <v>6 years</v>
+        <v>Preferred: Work From Home</v>
       </c>
       <c r="L3" t="str">
         <v>Indore</v>
@@ -567,65 +567,335 @@
         <v>NO</v>
       </c>
       <c r="O3" t="str">
-        <v>07-Sept-2026, 11:48 am</v>
-      </c>
-      <c r="P3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Tanmay Jain! 😊
-Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
-👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
-Please confirm (Yes / No or share your preferred time). 👍</v>
+        <v>16-Sept-2026, 11:23 am</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Social media manager and content writer and creator- work from home</v>
       </c>
       <c r="Q3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
+        <v>Garima Namdev</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+919713474209</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Experienced [Freelancer]</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O4" t="str">
+        <v>16-Sept-2026, 11:54 am</v>
+      </c>
+      <c r="P4" t="str">
+        <v>https://garimanamdevportfolio.my.canva.site/creative-portfolio GarimaNamdevResume.pdf</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Old</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+919876500002</v>
+      </c>
+      <c r="D5" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F5" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G5" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Not Interested</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O5" t="str">
+        <v>16-Sept-2026, 11:40 am</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Yes I want to apply now</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Rohit Sharma</v>
+      </c>
+      <c r="C6" t="str">
+        <v>+919876500001</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="G6" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Campaign Sent</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K6" t="str">
+        <v>1 years</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O6" t="str">
+        <v>16-Sept-2026, 11:40 am</v>
+      </c>
+      <c r="P6" t="str">
+        <v>1.5 years experience in reels, looking for work from home</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Outreach campaign broadcast sent</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C7" t="str">
+        <v>+918357977322</v>
+      </c>
+      <c r="D7" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="F7" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J7" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O7" t="str">
+        <v>07-Sept-2026, 1:26 pm</v>
+      </c>
+      <c r="P7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Arjun Meena! 🔔 *Interview Reminder*
+Your in-person interview for *SEO &amp; AEO Expert* at *Brand Setu Digital* is scheduled today at *Wed, 16 Sept, 11:00 am*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Ok sir" (In-Person)</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Tanmay Jain</v>
+      </c>
+      <c r="C8" t="str">
+        <v>+919993297342</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Digital Marketing Manager</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F8" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K8" t="str">
+        <v>6 years</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O8" t="str">
+        <v>07-Sept-2026, 11:48 am</v>
+      </c>
+      <c r="P8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Sure, Tanmay! This is a practical, in-person interview for the **Digital Marketing Manager** role at our Indore office. 
+During this round, you will have a brief discussion with our team, followed by a quick practical assessment to evaluate your campaign strategies and performance marketing skills. It will help us understand your hands-on experience with running ads and optimizing ROI. 
+Please let me know if tomorrow morning between *10:00 AM and 12:00 PM* works for you, or if you would like to suggest an alternative time! 👍🏢</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
         <v>Shyama's house of snacks</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C9" t="str">
         <v>+917693884339</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D9" t="str">
         <v>Digital Marketing Manager</v>
       </c>
-      <c r="E4" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F4" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
+      <c r="E9" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F9" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J9" t="str">
         <v>05-Sept-2026, 11:00 am</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K9" t="str">
         <v>Fresher (Paid Internship)</v>
       </c>
-      <c r="L4" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O4" t="str">
+      <c r="L9" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O9" t="str">
         <v>04-Sept-2026, 2:28 pm</v>
       </c>
-      <c r="P4" t="str" xml:space="preserve">
+      <c r="P9" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Shyama's house of snacks! 🔄
 Your interview for the *Digital Marketing Manager* position at *BrandSetu Digital* has been *rescheduled successfully*.
 📅 *Updated Date &amp; Time:* Sat, 5 Sept, 2026, 11:00 am
@@ -635,225 +905,225 @@
 See you then! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="Q9" t="str">
         <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
         <v>BrandSetuDigital</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C10" t="str">
         <v>+919669765911</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D10" t="str">
         <v>General Applicant</v>
       </c>
-      <c r="E5" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F5" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G5" t="str">
+      <c r="E10" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F10" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G10" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="J5" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M5" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O5" t="str">
+      <c r="J10" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O10" t="str">
         <v>04-Sept-2026, 2:33 pm</v>
       </c>
-      <c r="P5" t="str" xml:space="preserve">
+      <c r="P10" t="str" xml:space="preserve">
         <v xml:space="preserve">Namaste BrandSetuDigital! 👋
 BrandSetu Digital me *General Applicant* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
 👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
         <v>Mohit 🎬</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C11" t="str">
         <v>+917470584339</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D11" t="str">
         <v>Video Editor</v>
       </c>
-      <c r="E6" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F6" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G6" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
+      <c r="E11" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F11" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>Resume Received</v>
       </c>
-      <c r="J6" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N6" t="str">
-        <v>YES</v>
-      </c>
-      <c r="O6" t="str">
+      <c r="J11" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O11" t="str">
         <v>20-Aug-2026, 4:31 pm</v>
       </c>
-      <c r="P6" t="str" xml:space="preserve">
+      <c r="P11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Mohit! 😊
 Aapki profile aur portfolio HR team dwara shortlist kar li gayi hai. 👏✨
 👉 Kya aap kal morning me *10:00 AM se 12:00 PM* ke beech hamare Indore office (*103 Orange Business Park, Bhawarkua*) in-person interview ke liye aa sakte hain? 🏢
 Kripya confirm karein (Haan / Nahi ya apna suitable time batayein). 👍</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="Q11" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>manshi</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C12" t="str">
         <v>+917828966773</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D12" t="str">
         <v>Digital Marketing Manager</v>
       </c>
-      <c r="E7" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F7" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="E12" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F12" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G12" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="J7" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M7" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N7" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O7" t="str">
+      <c r="J12" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O12" t="str">
         <v>04-Sept-2026, 2:27 pm</v>
       </c>
-      <c r="P7" t="str" xml:space="preserve">
+      <c r="P12" t="str" xml:space="preserve">
         <v xml:space="preserve">Namaste manshi! 👋
 BrandSetu Digital me *Digital Marketing Manager* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
 👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
         <v>Aabid</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C13" t="str">
         <v>+917869724727</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D13" t="str">
         <v>AI Video Expert</v>
       </c>
-      <c r="E8" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F8" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G8" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
+      <c r="E13" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F13" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J13" t="str">
         <v>04-Sept-2026, 2:00 pm</v>
       </c>
-      <c r="K8" t="str">
+      <c r="K13" t="str">
         <v>Experienced (Full-Time)</v>
       </c>
-      <c r="L8" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M8" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N8" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O8" t="str">
+      <c r="L13" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O13" t="str">
         <v>04-Sept-2026, 2:15 pm</v>
       </c>
-      <c r="P8" t="str" xml:space="preserve">
+      <c r="P13" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Aabid! 🎉
 Your interview for the *AI Video Expert* position at *BrandSetu Digital* has been scheduled successfully.
 📅 *Date &amp; Time:* Fri, 4 Sept, 2026, 02:00 pm
@@ -863,57 +1133,57 @@
 Best of luck! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q13" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
+    <row r="14" xml:space="preserve">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
         <v>Nancy Ajmera</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C14" t="str">
         <v>+38899686625461</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D14" t="str">
         <v>General Applicant</v>
       </c>
-      <c r="E9" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F9" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="E14" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F14" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G14" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
         <v>Applied</v>
       </c>
-      <c r="J9" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M9" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N9" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O9" t="str">
+      <c r="J14" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M14" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O14" t="str">
         <v>03-Sept-2026, 5:03 pm</v>
       </c>
-      <c r="P9" t="str" xml:space="preserve">
+      <c r="P14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Nancy! 😊
 Welcome to Brand Setu Digital! 🎉
 We are actively hiring for:
@@ -925,272 +1195,6 @@
 6️⃣ 📢 *Digital Marketing Manager*
 👉 Which **position/role** would you like to apply for? (Please reply with number 1 to 6 or the role name) 📝</v>
       </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Unnat</v>
-      </c>
-      <c r="C10" t="str">
-        <v>+278880866857060</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F10" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G10" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H10" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="J10" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Experienced (Full-Time)</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N10" t="str">
-        <v>YES</v>
-      </c>
-      <c r="O10" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
-      </c>
-      <c r="P10" t="str">
-        <v>4 sep friday</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Arjun Meena</v>
-      </c>
-      <c r="C11" t="str">
-        <v>+919329232025</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F11" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G11" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H11" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="J11" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Fresher (Paid Internship)</v>
-      </c>
-      <c r="L11" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M11" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N11" t="str">
-        <v>YES</v>
-      </c>
-      <c r="O11" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
-      </c>
-      <c r="P11" t="str">
-        <v>Kal dopahar 2 baje</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>Test auto schedule</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Arjun Meena</v>
-      </c>
-      <c r="C12" t="str">
-        <v>+114405211672638</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F12" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G12" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="J12" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Fresher (Paid Internship)</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M12" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N12" t="str">
-        <v>YES</v>
-      </c>
-      <c r="O12" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
-      </c>
-      <c r="P12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Arjun! 😊
-Your interview is already confirmed for *Thu, 3 Sept, 05:00 pm* at 103 Orange Business Park, Bhawarkua, Indore. We look forward to meeting you! 😊📍</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>manisha</v>
-      </c>
-      <c r="C13" t="str">
-        <v>+917879010084</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F13" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G13" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>Resume Pending</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M13" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N13" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O13" t="str">
-        <v>20-Aug-2026, 3:49 pm</v>
-      </c>
-      <c r="P13" t="str">
-        <v>Hello manisha! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Annushka</v>
-      </c>
-      <c r="C14" t="str">
-        <v>+919039193109</v>
-      </c>
-      <c r="D14" t="str">
-        <v>General Applicant</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Full-Time</v>
-      </c>
-      <c r="F14" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G14" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>Resume Pending</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M14" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N14" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O14" t="str">
-        <v>10-Sept-2026, 12:45 pm</v>
-      </c>
-      <c r="P14" t="str">
-        <v>Hiiii</v>
-      </c>
       <c r="Q14" t="str">
         <v/>
       </c>
@@ -1200,13 +1204,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>सौमित्र</v>
+        <v>Unnat</v>
       </c>
       <c r="C15" t="str">
-        <v>+919770477701</v>
+        <v>+278880866857060</v>
       </c>
       <c r="D15" t="str">
-        <v>AI Video Expert</v>
+        <v>Video Editor</v>
       </c>
       <c r="E15" t="str">
         <v>Full-Time</v>
@@ -1215,37 +1219,37 @@
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="G15" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>https://corrra.com/@unnatportfolio</v>
       </c>
       <c r="I15" t="str">
-        <v>Not Interested</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="J15" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="L15" t="str">
         <v>Indore</v>
       </c>
       <c r="M15" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N15" t="str">
         <v>YES</v>
       </c>
       <c r="O15" t="str">
-        <v>12-Sept-2026, 2:49 pm</v>
+        <v>03-Sept-2026, 3:58 pm</v>
       </c>
       <c r="P15" t="str">
-        <v>Hi</v>
+        <v>4 sep friday</v>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
     <row r="16">
@@ -1253,34 +1257,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Candidate</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C16" t="str">
-        <v>+919876543211</v>
+        <v>+919329232025</v>
       </c>
       <c r="D16" t="str">
-        <v>Influencer Collaboration</v>
+        <v>Video Editor</v>
       </c>
       <c r="E16" t="str">
-        <v>Influencer Collaboration</v>
+        <v>Full-Time</v>
       </c>
       <c r="F16" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="G16" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="H16" t="str">
-        <v>Social: @tech_creator (45k)</v>
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
       </c>
       <c r="I16" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="J16" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="K16" t="str">
-        <v>Preferred: Influencer Collaboration</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="L16" t="str">
         <v>Indore</v>
@@ -1289,74 +1293,2031 @@
         <v>NO</v>
       </c>
       <c r="N16" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="O16" t="str">
-        <v>14-Sept-2026, 2:30 pm</v>
+        <v>03-Sept-2026, 3:35 pm</v>
       </c>
       <c r="P16" t="str">
-        <v>Hello, I want to connect for Influencer Collaboration. My instagram is @tech_creator with 45k followers</v>
+        <v>Kal dopahar 2 baje</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
+        <v>Test auto schedule</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Candidate</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C17" t="str">
-        <v>+919876543210</v>
+        <v>+114405211672638</v>
       </c>
       <c r="D17" t="str">
         <v>Video Editor</v>
       </c>
       <c r="E17" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F17" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G17" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J17" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M17" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N17" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O17" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="P17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Arjun! 😊
+Your interview is already confirmed for *Thu, 3 Sept, 05:00 pm* at 103 Orange Business Park, Bhawarkua, Indore. We look forward to meeting you! 😊📍</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C18" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F18" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G18" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M18" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N18" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O18" t="str">
+        <v>20-Aug-2026, 3:49 pm</v>
+      </c>
+      <c r="P18" t="str">
+        <v>Hello manisha! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Annushka</v>
+      </c>
+      <c r="C19" t="str">
+        <v>+919039193109</v>
+      </c>
+      <c r="D19" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F19" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G19" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M19" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N19" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O19" t="str">
+        <v>10-Sept-2026, 12:45 pm</v>
+      </c>
+      <c r="P19" t="str">
+        <v>Hiiii</v>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>सौमित्र</v>
+      </c>
+      <c r="C20" t="str">
+        <v>+919770477701</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="F20" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G20" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M20" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N20" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O20" t="str">
+        <v>12-Sept-2026, 2:49 pm</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Great! 🎬 Please share your updated *Resume (PDF)* and your Video Portfolio / Google Drive link here so we can evaluate your best work samples. 📄🎥</v>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C21" t="str">
+        <v>+919876543211</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="F21" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G21" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Social: @tech_creator (45k)</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Preferred: Influencer Collaboration</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M21" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N21" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O21" t="str">
+        <v>14-Sept-2026, 2:30 pm</v>
+      </c>
+      <c r="P21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Candidate! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Influencer Collaboration* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C22" t="str">
+        <v>+919876543210</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E22" t="str">
         <v>Freelancer</v>
       </c>
-      <c r="F17" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G17" t="str">
+      <c r="F22" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G22" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Preferred: Freelancer</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M22" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N22" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O22" t="str">
+        <v>14-Sept-2026, 2:30 pm</v>
+      </c>
+      <c r="P22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Candidate! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Video Editor* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Pooja Kimtee</v>
+      </c>
+      <c r="C23" t="str">
+        <v>+919098773689</v>
+      </c>
+      <c r="D23" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F23" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G23" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M23" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N23" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O23" t="str">
+        <v>15-Sept-2026, 1:49 pm</v>
+      </c>
+      <c r="P23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Pooja Kimtee! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Dileep Yadav</v>
+      </c>
+      <c r="C24" t="str">
+        <v>+916267343142</v>
+      </c>
+      <c r="D24" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F24" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G24" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M24" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N24" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O24" t="str">
+        <v>15-Sept-2026, 3:41 pm</v>
+      </c>
+      <c r="P24" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Dileep Yadav! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Salonipatel</v>
+      </c>
+      <c r="C25" t="str">
+        <v>+917879128725</v>
+      </c>
+      <c r="D25" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F25" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G25" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M25" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N25" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O25" t="str">
+        <v>15-Sept-2026, 3:58 pm</v>
+      </c>
+      <c r="P25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Salonipatel! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Rashi Agrawal Sm</v>
+      </c>
+      <c r="C26" t="str">
+        <v>+917067603800</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F26" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K26" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O26" t="str">
+        <v>15-Sept-2026, 4:02 pm</v>
+      </c>
+      <c r="P26" t="str">
+        <v>Great! 😊 We’ll be happy to have you. Please make sure to be available at the scheduled time. If you have any questions before the interview, feel free to message us.  See you soon! All the best. 🙌</v>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Himanshu Agnihotri</v>
+      </c>
+      <c r="C27" t="str">
+        <v>+919424011708</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F27" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G27" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K27" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M27" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N27" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O27" t="str">
+        <v>15-Sept-2026, 5:54 pm</v>
+      </c>
+      <c r="P27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Himanshu Agnihotri! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Saniya Soni</v>
+      </c>
+      <c r="C28" t="str">
+        <v>+919993829137</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Telecaller / Inside Sales</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F28" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G28" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J28" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K28" t="str">
+        <v>I have reached the location</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M28" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N28" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O28" t="str">
+        <v>15-Sept-2026, 6:17 pm</v>
+      </c>
+      <c r="P28" t="str">
+        <v>📍 *BrandSetu Digital Office Address:*103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014Google Maps: https://maps.google.com/?q=Orange+Business+Park+Indore</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Okay" (In-Person)</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Deepa Vishwakarma</v>
+      </c>
+      <c r="C29" t="str">
+        <v>+918965042108</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Part-Time</v>
+      </c>
+      <c r="F29" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G29" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Experienced [Part-Time]</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M29" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N29" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O29" t="str">
+        <v>15-Sept-2026, 6:45 pm</v>
+      </c>
+      <c r="P29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Deepa Vishwakarma! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Digitalwithpriyanshi</v>
+      </c>
+      <c r="C30" t="str">
+        <v>+918817289144</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Other Digital Marketing Roles</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F30" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G30" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Check on this please</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M30" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N30" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O30" t="str">
+        <v>15-Sept-2026, 7:19 pm</v>
+      </c>
+      <c r="P30" t="str">
+        <v>Dear Digitalwithpriyanshi! 🎉 Your in-person interview for the *Other Digital Marketing Roles* position is confirmed at our Indore office (103 Orange Business Park, Bhawarkua). Best of luck! 👍</v>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="C31" t="str">
+        <v>+919893433392</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F31" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G31" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J31" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Amit CV 2026.pdf</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M31" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N31" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O31" t="str">
+        <v>15-Sept-2026, 7:28 pm</v>
+      </c>
+      <c r="P31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Amit! 🔔 *Interview Reminder*
+Your in-person interview for *Graphic Designer* at *Brand Setu Digital* is scheduled today at *Wed, 16 Sept, 11:00 am*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Mahek Hablani</v>
+      </c>
+      <c r="C32" t="str">
+        <v>+918085393861</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F32" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G32" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J32" t="str">
+        <v>17-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K32" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O32" t="str">
+        <v>15-Sept-2026, 7:41 pm</v>
+      </c>
+      <c r="P32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Mahek Hablani! 🎉
+Your in-person interview for the *Social Media Manager* position at *BrandSetu Digital* has been scheduled successfully.
+📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 11:00 am
+📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
+📌 Please bring your updated Resume and work samples/portfolio.
+For any questions or directions, reply here or contact us at +91 9329232025.
+Best of luck! 👍
+- HR Team, BrandSetu Digital</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Day after tomorrow" (In-Person)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Ram Tanwar</v>
+      </c>
+      <c r="C33" t="str">
+        <v>+918770615526</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F33" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G33" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J33" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Preferred: Full-Time</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M33" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N33" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O33" t="str">
+        <v>15-Sept-2026, 8:30 pm</v>
+      </c>
+      <c r="P33" t="str">
+        <v>Great! Looking forward to seeing you at the interview. 👍 All the best! 😊</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Image</v>
+      </c>
+      <c r="C34" t="str">
+        <v>+918269011542</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="F34" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G34" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J34" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Fresher (Work From Home)</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M34" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N34" t="str">
+        <v>YES</v>
+      </c>
+      <c r="O34" t="str">
+        <v>15-Sept-2026, 8:44 pm</v>
+      </c>
+      <c r="P34" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Image! 🔔 *Interview Reminder*
+Your in-person interview for *Social Media Manager* at *Brand Setu Digital* is scheduled today at *Wed, 16 Sept, 11:00 am*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Okay" (In-Person)</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Sneha Patel</v>
+      </c>
+      <c r="C35" t="str">
+        <v>+919203383540</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="F35" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Preferred: Freelancer</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M35" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N35" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O35" t="str">
+        <v>15-Sept-2026, 8:48 pm</v>
+      </c>
+      <c r="P35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Sneha Patel! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Team Yamraj</v>
+      </c>
+      <c r="C36" t="str">
+        <v>+919770627922</v>
+      </c>
+      <c r="D36" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F36" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M36" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N36" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O36" t="str">
+        <v>15-Sept-2026, 8:56 pm</v>
+      </c>
+      <c r="P36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Team Yamraj! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Garima Namdev</v>
+      </c>
+      <c r="C37" t="str">
+        <v>+919713358457</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="F37" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G37" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O37" t="str">
+        <v>15-Sept-2026, 9:03 pm</v>
+      </c>
+      <c r="P37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Garima Namdev! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Rishi Sm</v>
+      </c>
+      <c r="C38" t="str">
+        <v>+919340297879</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F38" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G38" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J38" t="str">
+        <v>17-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Fresher (Freelancer)</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M38" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N38" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O38" t="str">
+        <v>15-Sept-2026, 9:32 pm</v>
+      </c>
+      <c r="P38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Rishi Sm! 🎉
+Your in-person interview for the *Social Media Manager* position at *BrandSetu Digital* has been scheduled successfully.
+📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 11:00 am
+📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
+📌 Please bring your updated Resume and work samples/portfolio.
+For any questions or directions, reply here or contact us at +91 9329232025.
+Best of luck! 👍
+- HR Team, BrandSetu Digital</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Pooja Tripathi</v>
+      </c>
+      <c r="C39" t="str">
+        <v>+916393680196</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F39" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M39" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N39" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O39" t="str">
+        <v>15-Sept-2026, 9:50 pm</v>
+      </c>
+      <c r="P39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Pooja Tripathi! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Ekta Talreja</v>
+      </c>
+      <c r="C40" t="str">
+        <v>+919179555776</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F40" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G40" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H40" t="str">
+        <v>https://docs.google.com/presentation/d/1i3b6HZMsPrEPYOjLO6-hyDBFZXplEPpMY5AfxGeo8Dk/edit?usp=sharing</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Fresher (Full-Time)</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O40" t="str">
+        <v>15-Sept-2026, 10:19 pm</v>
+      </c>
+      <c r="P40" t="str" xml:space="preserve">
+        <v xml:space="preserve">Thank you for sharing your resume/portfolio! 📄✨
+Our HR team is currently reviewing your profile and work samples. We will connect with you shortly for the next steps! 👍</v>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Khushi Malani</v>
+      </c>
+      <c r="C41" t="str">
+        <v>+918770389606</v>
+      </c>
+      <c r="D41" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F41" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G41" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J41" t="str">
+        <v>17-Sept-2026, 2:00 pm</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O41" t="str">
+        <v>15-Sept-2026, 10:53 pm</v>
+      </c>
+      <c r="P41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Khushi Malani! 🎉
+Your in-person interview for the *General Applicant* position at *BrandSetu Digital* has been scheduled successfully.
+📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 02:00 pm
+📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
+📌 Please bring your updated Resume and work samples/portfolio.
+For any questions or directions, reply here or contact us at +91 9329232025.
+Best of luck! 👍
+- HR Team, BrandSetu Digital</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Can interview be done at 2pm?" (In-Person)</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Nexora Labs</v>
+      </c>
+      <c r="C42" t="str">
+        <v>+918989051473</v>
+      </c>
+      <c r="D42" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F42" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G42" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M42" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N42" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O42" t="str">
+        <v>15-Sept-2026, 11:23 pm</v>
+      </c>
+      <c r="P42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Nexora Labs! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Mradul</v>
+      </c>
+      <c r="C43" t="str">
+        <v>+918602859616</v>
+      </c>
+      <c r="D43" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F43" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G43" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M43" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N43" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O43" t="str">
+        <v>15-Sept-2026, 11:47 pm</v>
+      </c>
+      <c r="P43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Mradul! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Lavvanya Joshi</v>
+      </c>
+      <c r="C44" t="str">
+        <v>+917770836080</v>
+      </c>
+      <c r="D44" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F44" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G44" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M44" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N44" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O44" t="str">
+        <v>16-Sept-2026, 12:23 am</v>
+      </c>
+      <c r="P44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Lavvanya Joshi! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C45" t="str">
+        <v>+918319029608</v>
+      </c>
+      <c r="D45" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F45" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G45" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J45" t="str">
+        <v>17-Sept-2026, 3:00 pm</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Preferred: Full-Time</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M45" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N45" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O45" t="str">
+        <v>16-Sept-2026, 12:48 am</v>
+      </c>
+      <c r="P45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Rahul! 🎉
+Your in-person interview for the *AI Video Expert* position at *BrandSetu Digital* has been scheduled successfully.
+📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 03:00 pm
+📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
+📌 Please bring your updated Resume and work samples/portfolio.
+For any questions or directions, reply here or contact us at +91 9329232025.
+Best of luck! 👍
+- HR Team, BrandSetu Digital</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Can I come at around 3 pm?" (In-Person)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Pradhyumn Kuril</v>
+      </c>
+      <c r="C46" t="str">
+        <v>+917828332884</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="F46" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G46" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J46" t="str">
+        <v>17-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Pradhyumn_Kuril_Resume_(1)[1].docx</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O46" t="str">
+        <v>16-Sept-2026, 12:54 am</v>
+      </c>
+      <c r="P46" t="str">
+        <v>ok</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes sure" (In-Person)</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Zainab Ansari</v>
+      </c>
+      <c r="C47" t="str">
+        <v>+916263807580</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F47" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G47" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M47" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N47" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O47" t="str">
+        <v>16-Sept-2026, 1:58 am</v>
+      </c>
+      <c r="P47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Zainab Ansari! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Somya Jain</v>
+      </c>
+      <c r="C48" t="str">
+        <v>+919131002563</v>
+      </c>
+      <c r="D48" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F48" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G48" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M48" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N48" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O48" t="str">
+        <v>16-Sept-2026, 2:27 am</v>
+      </c>
+      <c r="P48" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Somya Jain! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025)</v>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Khushi Dixit</v>
+      </c>
+      <c r="C49" t="str">
+        <v>+918982493940</v>
+      </c>
+      <c r="D49" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F49" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G49" t="str">
+        <v>YES</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M49" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N49" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O49" t="str">
+        <v>16-Sept-2026, 3:58 am</v>
+      </c>
+      <c r="P49" t="str">
+        <v>Dear Khushi Dixit! 🎉 Your in-person interview for the *General Applicant* position is confirmed at our Indore office (103 Orange Business Park, Bhawarkua). Best of luck! 👍</v>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Anjali</v>
+      </c>
+      <c r="C50" t="str">
+        <v>+919752628864</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="F50" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G50" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
         <v>Applied</v>
       </c>
-      <c r="J17" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Preferred: Freelancer</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M17" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N17" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O17" t="str">
-        <v>14-Sept-2026, 2:30 pm</v>
-      </c>
-      <c r="P17" t="str">
-        <v>Hi I am Rahul, I want to apply for video editor freelance work from home</v>
-      </c>
-      <c r="Q17" t="str">
+      <c r="J50" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Preferred: Influencer Collaboration</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M50" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N50" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O50" t="str">
+        <v>16-Sept-2026, 9:34 am</v>
+      </c>
+      <c r="P50" t="str" xml:space="preserve">
+        <v xml:space="preserve">Thank you for sharing your CV! 📄✨ 
+Our team is reviewing your profile and work samples. We will connect with you shortly for the next steps! 👍</v>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Rahul</v>
+      </c>
+      <c r="C51" t="str">
+        <v>+919753928315</v>
+      </c>
+      <c r="D51" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F51" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G51" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O51" t="str">
+        <v>16-Sept-2026, 10:40 am</v>
+      </c>
+      <c r="P51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Welcome to Brand Setu Digital! 🎉
+We are actively onboarding for these positions and collaborations:
+1️⃣ 🎬 *Video Editor*
+2️⃣ 🤖 *AI Video Expert*
+3️⃣ 🎨 *Graphic Designer*
+4️⃣ 🔎 *SEO &amp; AEO Expert*
+5️⃣ 📱 *Social Media Manager*
+6️⃣ 📢 *Digital Marketing Manager*
+7️⃣ ✨ *Influencer Collaboration!*
+💼 *Note:* If you are applying for any other *Digital Marketing Role* (SEO, SMM, Lead Gen, Content Writer, Web Developer, Telecaller, etc.), you can also reply with your role name.
+🌐 *Work Modes:* Full-Time (In-Office) | Work From Home (WFH) | Freelancer | Part-Time
+👉 Which **position or collaboration** would you like to apply for? (Please reply with number 1 to 7 or the name) 📝</v>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Poorva</v>
+      </c>
+      <c r="C52" t="str">
+        <v>+918982980773</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="F52" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G52" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Full-Time (1 year of experience) [Work From Home]</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O52" t="str">
+        <v>16-Sept-2026, 11:17 am</v>
+      </c>
+      <c r="P52" t="str">
+        <v>Super! 📱 Please share your updated *Resume (PDF)* and your past managed social media profiles / growth proof here. 📄🚀</v>
+      </c>
+      <c r="Q52" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q53"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -470,7 +470,7 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2">
         <v>1</v>
       </c>
@@ -516,8 +516,11 @@
       <c r="O2" t="str">
         <v>16-Sept-2026, 12:04 pm</v>
       </c>
-      <c r="P2" t="str">
-        <v>https://garimanamdevportfolio.my.canva.site/creative-portfolio GarimaNamdevResume.pdf</v>
+      <c r="P2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Garima Namdev! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -3315,9 +3318,84 @@
         <v/>
       </c>
     </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C53" t="str">
+        <v>+918085513390</v>
+      </c>
+      <c r="D53" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="F53" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="G53" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Campaign Sent</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="M53" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N53" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O53" t="str">
+        <v>16-Sept-2026, 12:17 pm</v>
+      </c>
+      <c r="P53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello! 👋_x000d_
+_x000d_
+Brand Setu Digital is expanding its Creative &amp; Marketing Team! 🚀_x000d_
+_x000d_
+We are currently hiring for multiple positions:_x000d_
+_x000d_
+1️⃣ Video Editor – Reels / YouTube 🎬_x000d_
+2️⃣ AI Video Expert – AI Tools / Prompting 🤖_x000d_
+3️⃣ Graphic Designer – Photoshop / Figma 🎨_x000d_
+4️⃣ SEO &amp; AEO Expert 🔎_x000d_
+5️⃣ Social Media Manager 📱_x000d_
+6️⃣ Digital Marketing Manager 📢_x000d_
+7️⃣ Influencer Collaboration ✨_x000d_
+_x000d_
+💼 Full-Time | Work From Home | Freelance opportunities are available._x000d_
+_x000d_
+If you’re interested, please share your updated Resume (PDF) and mention which position you are applying for._x000d_
+_x000d_
+👉 Example: “I’m applying for Position 1 – Video Editor.”_x000d_
+_x000d_
+If you’re interested in multiple positions, you can mention all the positions you’d like to apply for._x000d_
+_x000d_
+Our HR team will review your profile and get back to you with the next steps. 😊</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>Outreach campaign broadcast sent</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q53"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -579,7 +579,7 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4">
         <v>3</v>
       </c>
@@ -625,8 +625,11 @@
       <c r="O4" t="str">
         <v>16-Sept-2026, 11:54 am</v>
       </c>
-      <c r="P4" t="str">
-        <v>https://garimanamdevportfolio.my.canva.site/creative-portfolio GarimaNamdevResume.pdf</v>
+      <c r="P4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Garima Namdev! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -3173,7 +3176,7 @@
         <v/>
       </c>
       <c r="I50" t="str">
-        <v>Applied</v>
+        <v>Resume Pending</v>
       </c>
       <c r="J50" t="str">
         <v>Not Scheduled</v>
@@ -3185,7 +3188,7 @@
         <v>Indore</v>
       </c>
       <c r="M50" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N50" t="str">
         <v>NO</v>
@@ -3194,8 +3197,10 @@
         <v>16-Sept-2026, 9:34 am</v>
       </c>
       <c r="P50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Thank you for sharing your CV! 📄✨ 
-Our team is reviewing your profile and work samples. We will connect with you shortly for the next steps! 👍</v>
+        <v xml:space="preserve">Dear Anjali! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Influencer Collaboration* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
       </c>
       <c r="Q50" t="str">
         <v/>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,24 +397,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:V97"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="22.83203125" customWidth="1"/>
-    <col min="15" max="15" width="30.83203125" customWidth="1"/>
-    <col min="16" max="16" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="38.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="32.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="22.83203125" customWidth="1"/>
+    <col min="17" max="17" width="22.83203125" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" customWidth="1"/>
+    <col min="19" max="19" width="30.83203125" customWidth="1"/>
+    <col min="20" max="20" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,46 +435,61 @@
         <v>Role Applied</v>
       </c>
       <c r="E1" t="str">
-        <v>Work Mode</v>
+        <v>Experience</v>
       </c>
       <c r="F1" t="str">
-        <v>Interview Mode</v>
+        <v>Salary / Expectation</v>
       </c>
       <c r="G1" t="str">
-        <v>Resume Received</v>
+        <v>Interview Attended (Kab Aaya)</v>
       </c>
       <c r="H1" t="str">
-        <v>Portfolio / Drive / Social Link</v>
+        <v>Interview Date &amp; Time</v>
       </c>
       <c r="I1" t="str">
         <v>Candidate Status</v>
       </c>
       <c r="J1" t="str">
-        <v>Interview Date &amp; Time</v>
+        <v>Interview Feedback &amp; Description</v>
       </c>
       <c r="K1" t="str">
-        <v>Experience</v>
+        <v>Work Mode</v>
       </c>
       <c r="L1" t="str">
+        <v>Interview Mode</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Google Meet Link</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Requested Online Time</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Portfolio / Drive / Social Link</v>
+      </c>
+      <c r="Q1" t="str">
         <v>City</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>Resume Reminder Sent</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>Interview 1hr Reminder</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>Applied Date</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>Last Message</v>
       </c>
-      <c r="Q1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
+      <c r="V1" t="str">
+        <v>Internal Notes</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -484,154 +503,196 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E2" t="str">
-        <v>Freelancer</v>
+        <v>Experienced [Freelancer]</v>
       </c>
       <c r="F2" t="str">
-        <v>Online (Google Meet)</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I2" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R2" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S2" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T2" t="str">
+        <v>16-Sept-2026, 12:04 pm</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Dear Pranav Patil,  Congratulations! You have been shortlisted for the interview at BrandSetu Digital. We are pleased to invite you for the next round of the selection process.  📅 Date: 28/09/2026 ⏰ Time: 10:30 am                    📍Google Maps Location: https://maps.app.goo.gl/M6kv6SPc4rKMwj887?g_st=ic  Bhawarkua main road orange business park floor 103 mc donald's building, Indore  Please make sure to reach on time. For any assistance, feel free to contact us.  Looking forward to meeting you.  Warm regards, BrandSetu Digital</v>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Karishma Jaiswani</v>
+      </c>
+      <c r="C3" t="str">
+        <v>+918959264686</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Social Media Manager &amp; Content Writer</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Preferred: Work From Home</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H3" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P3" t="str">
+        <v>https://drive.google.com/file/d/1SGpoKwfEDMCdq2VH6pAPQgF7u1Xf_nmh/view?usp=drivesdk</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R3" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S3" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T3" t="str">
+        <v>16-Sept-2026, 11:23 am</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Social media manager and content writer and creator- work from home</v>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Garima Namdev</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+919713474209</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Experienced [Freelancer]</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H4" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="K2" t="str">
-        <v>Experienced [Freelancer]</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M2" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N2" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O2" t="str">
-        <v>16-Sept-2026, 12:04 pm</v>
-      </c>
-      <c r="P2" t="str" xml:space="preserve">
+      <c r="I4" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T4" t="str">
+        <v>16-Sept-2026, 11:54 am</v>
+      </c>
+      <c r="U4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Garima Namdev! 😊
 Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
 👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
 Please confirm (Yes / No or share your preferred time). 👍</v>
       </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Karishma Jaiswani</v>
-      </c>
-      <c r="C3" t="str">
-        <v>+918959264686</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Social Media Manager &amp; Content Writer</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Work From Home</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Online (Google Meet)</v>
-      </c>
-      <c r="G3" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H3" t="str">
-        <v>https://drive.google.com/file/d/1SGpoKwfEDMCdq2VH6pAPQgF7u1Xf_nmh/view?usp=drivesdk</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="J3" t="str">
-        <v>16-Sept-2026, 11:00 am</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Preferred: Work From Home</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M3" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N3" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O3" t="str">
-        <v>16-Sept-2026, 11:23 am</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Social media manager and content writer and creator- work from home</v>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Garima Namdev</v>
-      </c>
-      <c r="C4" t="str">
-        <v>+919713474209</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Social Media Manager</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Freelancer</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Online (Google Meet)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Resume Received</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Experienced [Freelancer]</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O4" t="str">
-        <v>16-Sept-2026, 11:54 am</v>
-      </c>
-      <c r="P4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Garima Namdev! 😊
-Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
-👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
-Please confirm (Yes / No or share your preferred time). 👍</v>
-      </c>
-      <c r="Q4" t="str">
+      <c r="V4" t="str">
         <v/>
       </c>
     </row>
@@ -649,42 +710,57 @@
         <v>General Applicant</v>
       </c>
       <c r="E5" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I5" t="str">
         <v>Not Interested</v>
       </c>
       <c r="J5" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L5" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M5" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N5" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O5" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T5" t="str">
         <v>16-Sept-2026, 11:40 am</v>
       </c>
-      <c r="P5" t="str">
-        <v>Yes I want to apply now</v>
-      </c>
-      <c r="Q5" t="str">
+      <c r="U5" t="str">
+        <v>Welcome to Brand Setu Digital! 🎉  We are actively onboarding for these positions and collaborations: 1️⃣ 🎬 Video Editor 2️⃣ 🤖 AI Video Expert 3️⃣ 🎨 Graphic Designer 4️⃣ 🔎 SEO &amp; AEO Expert 5️⃣ 📱 Social Media Manager 6️⃣ 📢 Digital Marketing Manager 7️⃣ ✨ Influencer Collaboration!  💼 Note: If you are applying for any other Digital Marketing Role (SEO, SMM, Lead Gen, Content Writer, Web Developer, Telecaller, etc.), you can also reply with your role name. 🌐 Work Modes: Full-Time (In-Office) | Work From Home (WFH) | Freelancer | Part-Time  👉 Which *position or collaboration* would you like to apply for? (Please reply with number 1 to 7 or the name) 📝</v>
+      </c>
+      <c r="V5" t="str">
         <v/>
       </c>
     </row>
@@ -702,46 +778,61 @@
         <v>Video Editor</v>
       </c>
       <c r="E6" t="str">
-        <v>Work From Home</v>
+        <v>1 years</v>
       </c>
       <c r="F6" t="str">
-        <v>Online (Google Meet)</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I6" t="str">
         <v>Campaign Sent</v>
       </c>
       <c r="J6" t="str">
-        <v>Not Scheduled</v>
+        <v>Outreach campaign broadcast sent</v>
       </c>
       <c r="K6" t="str">
-        <v>1 years</v>
+        <v>Work From Home</v>
       </c>
       <c r="L6" t="str">
-        <v>Indore</v>
+        <v>Online (Google Meet)</v>
       </c>
       <c r="M6" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N6" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O6" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R6" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T6" t="str">
         <v>16-Sept-2026, 11:40 am</v>
       </c>
-      <c r="P6" t="str">
-        <v>1.5 years experience in reels, looking for work from home</v>
-      </c>
-      <c r="Q6" t="str">
+      <c r="U6" t="str">
+        <v>Hello Rohit Sharma! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
+      </c>
+      <c r="V6" t="str">
         <v>Outreach campaign broadcast sent</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -755,48 +846,57 @@
         <v>SEO &amp; AEO Expert</v>
       </c>
       <c r="E7" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H7" t="str">
+        <v>16-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Ok sir" (In-Person)</v>
+      </c>
+      <c r="K7" t="str">
         <v>Freelancer</v>
       </c>
-      <c r="F7" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G7" t="str">
-        <v>YES</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="J7" t="str">
-        <v>16-Sept-2026, 11:00 am</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Experienced (Full-Time)</v>
-      </c>
       <c r="L7" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M7" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N7" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S7" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T7" t="str">
         <v>07-Sept-2026, 1:26 pm</v>
       </c>
-      <c r="P7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Arjun Meena! 🔔 *Interview Reminder*
-Your in-person interview for *SEO &amp; AEO Expert* at *Brand Setu Digital* is scheduled today at *Wed, 16 Sept, 11:00 am*.
-📍 *Office Address:*
-103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
-👉 Are you on your way to our office for the interview? Please confirm. 👍
-📞 Help/Directions: +91 9329232025
-- HR Team, Brand Setu Digital</v>
-      </c>
-      <c r="Q7" t="str">
+      <c r="U7" t="str">
+        <v>Dear Arjun Meena,Congratulations! You have been shortlisted for the interview at BrandSetu Digital.We are pleased to invite you for the next round of the selection process.📅 Date: 27/09/2026⏰ Time: 10:30 am                  📍Google Maps Location: https://maps.app.goo.gl/M6kv6SPc4rKMwj887?g_st=icBhawarkua main road orange business park floor 103 mc donald's building, IndorePlease make sure to reach on time.For any assistance, feel free to contact us.Looking forward to meeting you.Warm regards,BrandSetu Digital</v>
+      </c>
+      <c r="V7" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Ok sir" (In-Person)</v>
       </c>
     </row>
@@ -814,44 +914,59 @@
         <v>Digital Marketing Manager</v>
       </c>
       <c r="E8" t="str">
-        <v>Full-Time</v>
+        <v>6 years</v>
       </c>
       <c r="F8" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I8" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J8" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>6 years</v>
+        <v>Full-Time</v>
       </c>
       <c r="L8" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M8" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N8" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O8" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T8" t="str">
         <v>07-Sept-2026, 11:48 am</v>
       </c>
-      <c r="P8" t="str" xml:space="preserve">
+      <c r="U8" t="str" xml:space="preserve">
         <v xml:space="preserve">Sure, Tanmay! This is a practical, in-person interview for the **Digital Marketing Manager** role at our Indore office. 
 During this round, you will have a brief discussion with our team, followed by a quick practical assessment to evaluate your campaign strategies and performance marketing skills. It will help us understand your hands-on experience with running ads and optimizing ROI. 
 Please let me know if tomorrow morning between *10:00 AM and 12:00 PM* works for you, or if you would like to suggest an alternative time! 👍🏢</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="V8" t="str">
         <v/>
       </c>
     </row>
@@ -869,39 +984,54 @@
         <v>Digital Marketing Manager</v>
       </c>
       <c r="E9" t="str">
-        <v>Full-Time</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="F9" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>05-Sept-2026, 11:00 am</v>
       </c>
       <c r="I9" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J9" t="str">
-        <v>05-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
       </c>
       <c r="K9" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L9" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M9" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N9" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T9" t="str">
         <v>04-Sept-2026, 2:28 pm</v>
       </c>
-      <c r="P9" t="str" xml:space="preserve">
+      <c r="U9" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Shyama's house of snacks! 🔄
 Your interview for the *Digital Marketing Manager* position at *BrandSetu Digital* has been *rescheduled successfully*.
 📅 *Updated Date &amp; Time:* Sat, 5 Sept, 2026, 11:00 am
@@ -911,11 +1041,11 @@
 See you then! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="V9" t="str">
         <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -929,49 +1059,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E10" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I10" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J10" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L10" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M10" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N10" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O10" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T10" t="str">
         <v>04-Sept-2026, 2:33 pm</v>
       </c>
-      <c r="P10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Namaste BrandSetuDigital! 👋
-BrandSetu Digital me *General Applicant* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
-👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
+      <c r="U10" t="str">
+        <v>Hello Candidate! 😊 Aapne BrandSetu Digital me job ke liye connect kiya tha. Kripya batayein aap inme se kis position ke liye apply karna chahte hain? (1. Video Editor, 2. AI Video Expert, 3. Graphic Designer, 4. SEO &amp; AEO Expert, 5. Social Media Manager, 6. Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -985,45 +1127,57 @@
         <v>Video Editor</v>
       </c>
       <c r="E11" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I11" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J11" t="str">
-        <v>Not Scheduled</v>
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L11" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M11" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N11" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T11" t="str">
         <v>20-Aug-2026, 4:31 pm</v>
       </c>
-      <c r="P11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Mohit! 😊
-Aapki profile aur portfolio HR team dwara shortlist kar li gayi hai. 👏✨
-👉 Kya aap kal morning me *10:00 AM se 12:00 PM* ke beech hamare Indore office (*103 Orange Business Park, Bhawarkua*) in-person interview ke liye aa sakte hain? 🏢
-Kripya confirm karein (Haan / Nahi ya apna suitable time batayein). 👍</v>
-      </c>
-      <c r="Q11" t="str">
+      <c r="U11" t="str">
+        <v>Hello Mohit! 😊 BrandSetu Digital me *Video Editor* position ke liye: Kripya batayein aap Fresher hain ya Experienced? Aur aapke core skills ya tools kya hain? 💼</v>
+      </c>
+      <c r="V11" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
@@ -1038,48 +1192,61 @@
         <v>+917828966773</v>
       </c>
       <c r="D12" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>Graphic Designer</v>
       </c>
       <c r="E12" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <v>Full-Time</v>
       </c>
-      <c r="F12" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G12" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>Resume Pending</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
       <c r="L12" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M12" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N12" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T12" t="str">
         <v>04-Sept-2026, 2:27 pm</v>
       </c>
-      <c r="P12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Namaste manshi! 👋
-BrandSetu Digital me *Digital Marketing Manager* position ke liye aapke interest ke liye dhanyawad. Humein abhi tak aapka updated *Resume / Portfolio* receive nahi hua hai. 📄
-👉 Kripya apna Resume (PDF) ya Portfolio link yahan share karein taaki hum aapka interview schedule kar sakein. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q12" t="str">
+      <c r="U12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Thank you for sharing your resume/portfolio! 📄✨
+Our HR team is currently reviewing your profile and work samples. We will connect with you shortly for the next steps! 👍</v>
+      </c>
+      <c r="V12" t="str">
         <v/>
       </c>
     </row>
@@ -1097,39 +1264,54 @@
         <v>AI Video Expert</v>
       </c>
       <c r="E13" t="str">
-        <v>Full-Time</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="F13" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="I13" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J13" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
       <c r="K13" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L13" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M13" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N13" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T13" t="str">
         <v>04-Sept-2026, 2:15 pm</v>
       </c>
-      <c r="P13" t="str" xml:space="preserve">
+      <c r="U13" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Aabid! 🎉
 Your interview for the *AI Video Expert* position at *BrandSetu Digital* has been scheduled successfully.
 📅 *Date &amp; Time:* Fri, 4 Sept, 2026, 02:00 pm
@@ -1139,7 +1321,7 @@
 Best of luck! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="V13" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
@@ -1157,39 +1339,54 @@
         <v>General Applicant</v>
       </c>
       <c r="E14" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I14" t="str">
         <v>Applied</v>
       </c>
       <c r="J14" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L14" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M14" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N14" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O14" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R14" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T14" t="str">
         <v>03-Sept-2026, 5:03 pm</v>
       </c>
-      <c r="P14" t="str" xml:space="preserve">
+      <c r="U14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Nancy! 😊
 Welcome to Brand Setu Digital! 🎉
 We are actively hiring for:
@@ -1201,7 +1398,7 @@
 6️⃣ 📢 *Digital Marketing Manager*
 👉 Which **position/role** would you like to apply for? (Please reply with number 1 to 6 or the role name) 📝</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="V14" t="str">
         <v/>
       </c>
     </row>
@@ -1219,42 +1416,57 @@
         <v>Video Editor</v>
       </c>
       <c r="E15" t="str">
-        <v>Full-Time</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="F15" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H15" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="I15" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J15" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
       <c r="K15" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L15" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M15" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N15" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O15" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P15" t="str">
+        <v>https://corrra.com/@unnatportfolio</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R15" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S15" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T15" t="str">
         <v>03-Sept-2026, 3:58 pm</v>
       </c>
-      <c r="P15" t="str">
+      <c r="U15" t="str">
         <v>4 sep friday</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="V15" t="str">
         <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
@@ -1272,42 +1484,57 @@
         <v>Video Editor</v>
       </c>
       <c r="E16" t="str">
-        <v>Full-Time</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="F16" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H16" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="I16" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J16" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Test auto schedule</v>
       </c>
       <c r="K16" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L16" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M16" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N16" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O16" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P16" t="str">
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R16" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S16" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T16" t="str">
         <v>03-Sept-2026, 3:35 pm</v>
       </c>
-      <c r="P16" t="str">
+      <c r="U16" t="str">
         <v>Kal dopahar 2 baje</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="V16" t="str">
         <v>Test auto schedule</v>
       </c>
     </row>
@@ -1325,43 +1552,58 @@
         <v>Video Editor</v>
       </c>
       <c r="E17" t="str">
-        <v>Full-Time</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="F17" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>03-Sept-2026, 5:00 pm</v>
       </c>
       <c r="I17" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J17" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
       </c>
       <c r="K17" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L17" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M17" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N17" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O17" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R17" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S17" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T17" t="str">
         <v>03-Sept-2026, 2:29 pm</v>
       </c>
-      <c r="P17" t="str" xml:space="preserve">
+      <c r="U17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Arjun! 😊
 Your interview is already confirmed for *Thu, 3 Sept, 05:00 pm* at 103 Orange Business Park, Bhawarkua, Indore. We look forward to meeting you! 😊📍</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="V17" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
       </c>
     </row>
@@ -1379,42 +1621,57 @@
         <v>Video Editor</v>
       </c>
       <c r="E18" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I18" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J18" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L18" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M18" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N18" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O18" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R18" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S18" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T18" t="str">
         <v>20-Aug-2026, 3:49 pm</v>
       </c>
-      <c r="P18" t="str">
-        <v>Hello manisha! 😊 Please share your updated *Resume (PDF)* or Portfolio/Drive link here so we can proceed with your application! 📄💼</v>
-      </c>
-      <c r="Q18" t="str">
+      <c r="U18" t="str">
+        <v>Hello Manisha! 😊 BrandSetu Digital me *Video Editor* position ke liye: Kripya batayein aap Fresher hain ya Experienced? Aur aapke core skills ya tools kya hain? 💼</v>
+      </c>
+      <c r="V18" t="str">
         <v/>
       </c>
     </row>
@@ -1432,42 +1689,57 @@
         <v>General Applicant</v>
       </c>
       <c r="E19" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I19" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J19" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L19" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M19" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N19" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O19" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R19" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S19" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T19" t="str">
         <v>10-Sept-2026, 12:45 pm</v>
       </c>
-      <c r="P19" t="str">
-        <v>Hiiii</v>
-      </c>
-      <c r="Q19" t="str">
+      <c r="U19" t="str">
+        <v>Hello Annushka! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V19" t="str">
         <v/>
       </c>
     </row>
@@ -1485,46 +1757,61 @@
         <v>Video Editor</v>
       </c>
       <c r="E20" t="str">
-        <v>Influencer Collaboration</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="F20" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I20" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J20" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="L20" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M20" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N20" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O20" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R20" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S20" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T20" t="str">
         <v>12-Sept-2026, 2:49 pm</v>
       </c>
-      <c r="P20" t="str">
+      <c r="U20" t="str">
         <v>Great! 🎬 Please share your updated *Resume (PDF)* and your Video Portfolio / Google Drive link here so we can evaluate your best work samples. 📄🎥</v>
       </c>
-      <c r="Q20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
+      <c r="V20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1538,49 +1825,61 @@
         <v>Influencer Collaboration</v>
       </c>
       <c r="E21" t="str">
-        <v>Influencer Collaboration</v>
+        <v>Preferred: Influencer Collaboration</v>
       </c>
       <c r="F21" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H21" t="str">
-        <v>Social: @tech_creator (45k)</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I21" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J21" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K21" t="str">
-        <v>Preferred: Influencer Collaboration</v>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="L21" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M21" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N21" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O21" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Social: @tech_creator (45k)</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R21" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S21" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T21" t="str">
         <v>14-Sept-2026, 2:30 pm</v>
       </c>
-      <c r="P21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Candidate! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *Influencer Collaboration* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
+      <c r="U21" t="str">
+        <v>Hello, I want to connect for Influencer Collaboration. My instagram is @tech_creator with 45k followers</v>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1594,49 +1893,61 @@
         <v>Video Editor</v>
       </c>
       <c r="E22" t="str">
-        <v>Freelancer</v>
+        <v>Preferred: Freelancer</v>
       </c>
       <c r="F22" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I22" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J22" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K22" t="str">
-        <v>Preferred: Freelancer</v>
+        <v>Freelancer</v>
       </c>
       <c r="L22" t="str">
-        <v>Indore</v>
+        <v>Online (Google Meet)</v>
       </c>
       <c r="M22" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N22" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O22" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R22" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S22" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T22" t="str">
         <v>14-Sept-2026, 2:30 pm</v>
       </c>
-      <c r="P22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Candidate! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *Video Editor* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
+      <c r="U22" t="str">
+        <v>Hi I am Rahul, I want to apply for video editor freelance work from home</v>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1650,49 +1961,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E23" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I23" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J23" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L23" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M23" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N23" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O23" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R23" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S23" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T23" t="str">
         <v>15-Sept-2026, 1:49 pm</v>
       </c>
-      <c r="P23" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Pooja Kimtee! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
+      <c r="U23" t="str">
+        <v>Hello Pooja Kimtee! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1706,49 +2029,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E24" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I24" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J24" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L24" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M24" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N24" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O24" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R24" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S24" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T24" t="str">
         <v>15-Sept-2026, 3:41 pm</v>
       </c>
-      <c r="P24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Dileep Yadav! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
+      <c r="U24" t="str">
+        <v>Hello Dileep Yadav! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1762,45 +2097,57 @@
         <v>General Applicant</v>
       </c>
       <c r="E25" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I25" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J25" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L25" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M25" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N25" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O25" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R25" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S25" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T25" t="str">
         <v>15-Sept-2026, 3:58 pm</v>
       </c>
-      <c r="P25" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Salonipatel! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q25" t="str">
+      <c r="U25" t="str">
+        <v>Hello Salonipatel! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V25" t="str">
         <v/>
       </c>
     </row>
@@ -1818,42 +2165,57 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E26" t="str">
-        <v>Full-Time</v>
+        <v>5 years</v>
       </c>
       <c r="F26" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I26" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J26" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>5 years</v>
+        <v>Full-Time</v>
       </c>
       <c r="L26" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M26" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N26" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O26" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T26" t="str">
         <v>15-Sept-2026, 4:02 pm</v>
       </c>
-      <c r="P26" t="str">
+      <c r="U26" t="str">
         <v>Great! 😊 We’ll be happy to have you. Please make sure to be available at the scheduled time. If you have any questions before the interview, feel free to message us.  See you soon! All the best. 🙌</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="V26" t="str">
         <v/>
       </c>
     </row>
@@ -1871,45 +2233,60 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E27" t="str">
-        <v>Full-Time</v>
+        <v>5 years</v>
       </c>
       <c r="F27" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I27" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J27" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>5 years</v>
+        <v>Full-Time</v>
       </c>
       <c r="L27" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M27" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N27" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O27" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R27" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S27" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T27" t="str">
         <v>15-Sept-2026, 5:54 pm</v>
       </c>
-      <c r="P27" t="str" xml:space="preserve">
+      <c r="U27" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Himanshu Agnihotri! 👋
 Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
 👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="V27" t="str">
         <v/>
       </c>
     </row>
@@ -1927,42 +2304,57 @@
         <v>Telecaller / Inside Sales</v>
       </c>
       <c r="E28" t="str">
-        <v>Full-Time</v>
+        <v>I have reached the location</v>
       </c>
       <c r="F28" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>16-Sept-2026, 11:00 am</v>
       </c>
       <c r="I28" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J28" t="str">
-        <v>16-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Okay" (In-Person)</v>
       </c>
       <c r="K28" t="str">
-        <v>I have reached the location</v>
+        <v>Full-Time</v>
       </c>
       <c r="L28" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M28" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N28" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O28" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R28" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S28" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T28" t="str">
         <v>15-Sept-2026, 6:17 pm</v>
       </c>
-      <c r="P28" t="str">
+      <c r="U28" t="str">
         <v>📍 *BrandSetu Digital Office Address:*103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014Google Maps: https://maps.google.com/?q=Orange+Business+Park+Indore</v>
       </c>
-      <c r="Q28" t="str">
+      <c r="V28" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Okay" (In-Person)</v>
       </c>
     </row>
@@ -1980,45 +2372,60 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E29" t="str">
-        <v>Part-Time</v>
+        <v>Experienced [Part-Time]</v>
       </c>
       <c r="F29" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I29" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J29" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K29" t="str">
-        <v>Experienced [Part-Time]</v>
+        <v>Part-Time</v>
       </c>
       <c r="L29" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M29" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N29" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O29" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R29" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S29" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T29" t="str">
         <v>15-Sept-2026, 6:45 pm</v>
       </c>
-      <c r="P29" t="str" xml:space="preserve">
+      <c r="U29" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Deepa Vishwakarma! 👋
 Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
 👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="V29" t="str">
         <v/>
       </c>
     </row>
@@ -2036,42 +2443,57 @@
         <v>Other Digital Marketing Roles</v>
       </c>
       <c r="E30" t="str">
-        <v>Full-Time</v>
+        <v>Check on this please</v>
       </c>
       <c r="F30" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I30" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J30" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K30" t="str">
-        <v>Check on this please</v>
+        <v>Full-Time</v>
       </c>
       <c r="L30" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M30" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N30" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O30" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R30" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S30" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T30" t="str">
         <v>15-Sept-2026, 7:19 pm</v>
       </c>
-      <c r="P30" t="str">
+      <c r="U30" t="str">
         <v>Dear Digitalwithpriyanshi! 🎉 Your in-person interview for the *Other Digital Marketing Roles* position is confirmed at our Indore office (103 Orange Business Park, Bhawarkua). Best of luck! 👍</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="V30" t="str">
         <v/>
       </c>
     </row>
@@ -2089,39 +2511,54 @@
         <v>Graphic Designer</v>
       </c>
       <c r="E31" t="str">
-        <v>Full-Time</v>
+        <v>Amit CV 2026.pdf</v>
       </c>
       <c r="F31" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>16-Sept-2026, 11:00 am</v>
       </c>
       <c r="I31" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J31" t="str">
-        <v>16-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
       <c r="K31" t="str">
-        <v>Amit CV 2026.pdf</v>
+        <v>Full-Time</v>
       </c>
       <c r="L31" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M31" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O31" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R31" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S31" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T31" t="str">
         <v>15-Sept-2026, 7:28 pm</v>
       </c>
-      <c r="P31" t="str" xml:space="preserve">
+      <c r="U31" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Amit! 🔔 *Interview Reminder*
 Your in-person interview for *Graphic Designer* at *Brand Setu Digital* is scheduled today at *Wed, 16 Sept, 11:00 am*.
 📍 *Office Address:*
@@ -2130,7 +2567,7 @@
 📞 Help/Directions: +91 9329232025
 - HR Team, Brand Setu Digital</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="V31" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
     </row>
@@ -2148,39 +2585,54 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E32" t="str">
-        <v>Full-Time</v>
+        <v>5 years</v>
       </c>
       <c r="F32" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G32" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>17-Sept-2026, 11:00 am</v>
       </c>
       <c r="I32" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J32" t="str">
-        <v>17-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Day after tomorrow" (In-Person)</v>
       </c>
       <c r="K32" t="str">
-        <v>5 years</v>
+        <v>Full-Time</v>
       </c>
       <c r="L32" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M32" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O32" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T32" t="str">
         <v>15-Sept-2026, 7:41 pm</v>
       </c>
-      <c r="P32" t="str" xml:space="preserve">
+      <c r="U32" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Mahek Hablani! 🎉
 Your in-person interview for the *Social Media Manager* position at *BrandSetu Digital* has been scheduled successfully.
 📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 11:00 am
@@ -2190,7 +2642,7 @@
 Best of luck! 👍
 - HR Team, BrandSetu Digital</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="V32" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Day after tomorrow" (In-Person)</v>
       </c>
     </row>
@@ -2208,42 +2660,57 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E33" t="str">
-        <v>Full-Time</v>
+        <v>Preferred: Full-Time</v>
       </c>
       <c r="F33" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>16-Sept-2026, 11:00 am</v>
       </c>
       <c r="I33" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J33" t="str">
-        <v>16-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
       <c r="K33" t="str">
-        <v>Preferred: Full-Time</v>
+        <v>Full-Time</v>
       </c>
       <c r="L33" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M33" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O33" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R33" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S33" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T33" t="str">
         <v>15-Sept-2026, 8:30 pm</v>
       </c>
-      <c r="P33" t="str">
+      <c r="U33" t="str">
         <v>Great! Looking forward to seeing you at the interview. 👍 All the best! 😊</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="V33" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
     </row>
@@ -2261,39 +2728,54 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E34" t="str">
-        <v>Work From Home</v>
+        <v>Fresher (Work From Home)</v>
       </c>
       <c r="F34" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G34" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>16-Sept-2026, 11:00 am</v>
       </c>
       <c r="I34" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J34" t="str">
-        <v>16-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Okay" (In-Person)</v>
       </c>
       <c r="K34" t="str">
-        <v>Fresher (Work From Home)</v>
+        <v>Work From Home</v>
       </c>
       <c r="L34" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M34" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="O34" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R34" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S34" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T34" t="str">
         <v>15-Sept-2026, 8:44 pm</v>
       </c>
-      <c r="P34" t="str" xml:space="preserve">
+      <c r="U34" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Image! 🔔 *Interview Reminder*
 Your in-person interview for *Social Media Manager* at *Brand Setu Digital* is scheduled today at *Wed, 16 Sept, 11:00 am*.
 📍 *Office Address:*
@@ -2302,7 +2784,7 @@
 📞 Help/Directions: +91 9329232025
 - HR Team, Brand Setu Digital</v>
       </c>
-      <c r="Q34" t="str">
+      <c r="V34" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Okay" (In-Person)</v>
       </c>
     </row>
@@ -2320,49 +2802,64 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E35" t="str">
-        <v>Freelancer</v>
+        <v>Preferred: Freelancer</v>
       </c>
       <c r="F35" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I35" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J35" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K35" t="str">
-        <v>Preferred: Freelancer</v>
+        <v>Freelancer</v>
       </c>
       <c r="L35" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M35" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O35" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R35" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S35" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T35" t="str">
         <v>15-Sept-2026, 8:48 pm</v>
       </c>
-      <c r="P35" t="str" xml:space="preserve">
+      <c r="U35" t="str" xml:space="preserve">
         <v xml:space="preserve">Hello Sneha Patel! 👋
 Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
 👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025)</v>
       </c>
-      <c r="Q35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
+      <c r="V35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2376,49 +2873,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E36" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I36" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J36" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K36" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L36" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M36" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O36" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R36" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S36" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T36" t="str">
         <v>15-Sept-2026, 8:56 pm</v>
       </c>
-      <c r="P36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Team Yamraj! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
+      <c r="U36" t="str">
+        <v>Hello Team Yamraj! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2432,45 +2941,57 @@
         <v>Graphic Designer</v>
       </c>
       <c r="E37" t="str">
-        <v>Freelancer</v>
+        <v/>
       </c>
       <c r="F37" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I37" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J37" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>Freelancer</v>
       </c>
       <c r="L37" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M37" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O37" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T37" t="str">
         <v>15-Sept-2026, 9:03 pm</v>
       </c>
-      <c r="P37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Garima Namdev! 😊
-Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
-👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
-Please confirm (Yes / No or share your preferred time). 👍</v>
-      </c>
-      <c r="Q37" t="str">
+      <c r="U37" t="str">
+        <v>Hello Garima Namdev! 😊 Regarding your application for *Graphic Designer* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V37" t="str">
         <v/>
       </c>
     </row>
@@ -2488,53 +3009,67 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E38" t="str">
-        <v>Full-Time</v>
+        <v>Fresher (Freelancer)</v>
       </c>
       <c r="F38" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G38" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>17-Sept-2026, 11:00 am</v>
       </c>
       <c r="I38" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J38" t="str">
-        <v>17-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
       <c r="K38" t="str">
-        <v>Fresher (Freelancer)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L38" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M38" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O38" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R38" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S38" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T38" t="str">
         <v>15-Sept-2026, 9:32 pm</v>
       </c>
-      <c r="P38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear Rishi Sm! 🎉
-Your in-person interview for the *Social Media Manager* position at *BrandSetu Digital* has been scheduled successfully.
-📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 11:00 am
-📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
-📌 Please bring your updated Resume and work samples/portfolio.
-For any questions or directions, reply here or contact us at +91 9329232025.
-Best of luck! 👍
-- HR Team, BrandSetu Digital</v>
-      </c>
-      <c r="Q38" t="str">
+      <c r="U38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Rishi Sm! 🔔 *Interview Reminder*
+Your in-person interview for *Social Media Manager* at *Brand Setu Digital* is scheduled today at *Thu, 17 Sept, 11:00 am*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V38" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
     </row>
-    <row r="39" xml:space="preserve">
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2548,45 +3083,57 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E39" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F39" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G39" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I39" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J39" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L39" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M39" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N39" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O39" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R39" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S39" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T39" t="str">
         <v>15-Sept-2026, 9:50 pm</v>
       </c>
-      <c r="P39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Pooja Tripathi! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q39" t="str">
+      <c r="U39" t="str">
+        <v>Hello Pooja Tripathi! 😊 Regarding your application for *Social Media Manager* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V39" t="str">
         <v/>
       </c>
     </row>
@@ -2604,47 +3151,62 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E40" t="str">
-        <v>Full-Time</v>
+        <v>Fresher (Full-Time)</v>
       </c>
       <c r="F40" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H40" t="str">
-        <v>https://docs.google.com/presentation/d/1i3b6HZMsPrEPYOjLO6-hyDBFZXplEPpMY5AfxGeo8Dk/edit?usp=sharing</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I40" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J40" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K40" t="str">
-        <v>Fresher (Full-Time)</v>
+        <v>Full-Time</v>
       </c>
       <c r="L40" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M40" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O40" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P40" t="str">
+        <v>https://docs.google.com/presentation/d/1i3b6HZMsPrEPYOjLO6-hyDBFZXplEPpMY5AfxGeo8Dk/edit?usp=sharing</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T40" t="str">
         <v>15-Sept-2026, 10:19 pm</v>
       </c>
-      <c r="P40" t="str" xml:space="preserve">
+      <c r="U40" t="str" xml:space="preserve">
         <v xml:space="preserve">Thank you for sharing your resume/portfolio! 📄✨
 Our HR team is currently reviewing your profile and work samples. We will connect with you shortly for the next steps! 👍</v>
       </c>
-      <c r="Q40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
+      <c r="V40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2658,53 +3220,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E41" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G41" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>17-Sept-2026, 5:00 pm</v>
       </c>
       <c r="I41" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J41" t="str">
-        <v>17-Sept-2026, 2:00 pm</v>
+        <v>Auto-scheduled via WhatsApp AI: "Today is 17th September" (Online Google Meet)</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L41" t="str">
-        <v>Indore</v>
+        <v>Online (Google Meet)</v>
       </c>
       <c r="M41" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N41" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O41" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T41" t="str">
         <v>15-Sept-2026, 10:53 pm</v>
       </c>
-      <c r="P41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear Khushi Malani! 🎉
-Your in-person interview for the *General Applicant* position at *BrandSetu Digital* has been scheduled successfully.
-📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 02:00 pm
-📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
-📌 Please bring your updated Resume and work samples/portfolio.
-For any questions or directions, reply here or contact us at +91 9329232025.
-Best of luck! 👍
-- HR Team, BrandSetu Digital</v>
-      </c>
-      <c r="Q41" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Can interview be done at 2pm?" (In-Person)</v>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
+      <c r="U41" t="str">
+        <v>Ok</v>
+      </c>
+      <c r="V41" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today is 17th September" (Online Google Meet)</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2718,49 +3288,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E42" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I42" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J42" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K42" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L42" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M42" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N42" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O42" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R42" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S42" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T42" t="str">
         <v>15-Sept-2026, 11:23 pm</v>
       </c>
-      <c r="P42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Nexora Labs! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
+      <c r="U42" t="str">
+        <v>Hello Nexora Labs! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2774,49 +3356,61 @@
         <v>General Applicant</v>
       </c>
       <c r="E43" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G43" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I43" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J43" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L43" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M43" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N43" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O43" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R43" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S43" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T43" t="str">
         <v>15-Sept-2026, 11:47 pm</v>
       </c>
-      <c r="P43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Mradul! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
+      <c r="U43" t="str">
+        <v>Hello Mradul! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2830,45 +3424,57 @@
         <v>General Applicant</v>
       </c>
       <c r="E44" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G44" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I44" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J44" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L44" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M44" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N44" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O44" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R44" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S44" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T44" t="str">
         <v>16-Sept-2026, 12:23 am</v>
       </c>
-      <c r="P44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Lavvanya Joshi! 😊
-Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
-👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
-Please confirm (Yes / No or share your preferred time). 👍</v>
-      </c>
-      <c r="Q44" t="str">
+      <c r="U44" t="str">
+        <v>Hello Lavvanya Joshi! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V44" t="str">
         <v/>
       </c>
     </row>
@@ -2886,50 +3492,64 @@
         <v>AI Video Expert</v>
       </c>
       <c r="E45" t="str">
-        <v>Full-Time</v>
+        <v>Preferred: Full-Time</v>
       </c>
       <c r="F45" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>19-Sept-2026, 11:00 am</v>
       </c>
       <c r="I45" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J45" t="str">
-        <v>17-Sept-2026, 3:00 pm</v>
+        <v>Auto-scheduled via WhatsApp AI: "Can I come tomorrow for the interview?" (In-Person)</v>
       </c>
       <c r="K45" t="str">
-        <v>Preferred: Full-Time</v>
+        <v>Full-Time</v>
       </c>
       <c r="L45" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M45" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N45" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O45" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R45" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S45" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T45" t="str">
         <v>16-Sept-2026, 12:48 am</v>
       </c>
-      <c r="P45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear Rahul! 🎉
-Your in-person interview for the *AI Video Expert* position at *BrandSetu Digital* has been scheduled successfully.
-📅 *Date &amp; Time:* Thu, 17 Sept, 2026, 03:00 pm
-📍 *Office Address:* 103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Transport Nagar, Indore (M.P.) - 452014
-📌 Please bring your updated Resume and work samples/portfolio.
-For any questions or directions, reply here or contact us at +91 9329232025.
-Best of luck! 👍
-- HR Team, BrandSetu Digital</v>
-      </c>
-      <c r="Q45" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Can I come at around 3 pm?" (In-Person)</v>
+      <c r="U45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Rahul! 🔔 *Interview Reminder*
+Your in-person interview for *AI Video Expert* at *Brand Setu Digital* is scheduled today at *Sat, 19 Sept, 11:00 am*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V45" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Can I come tomorrow for the interview?" (In-Person)</v>
       </c>
     </row>
     <row r="46">
@@ -2946,42 +3566,57 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E46" t="str">
-        <v>Work From Home</v>
+        <v>Pradhyumn_Kuril_Resume_(1)[1].docx</v>
       </c>
       <c r="F46" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G46" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>17-Sept-2026, 11:00 am</v>
       </c>
       <c r="I46" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="J46" t="str">
-        <v>17-Sept-2026, 11:00 am</v>
+        <v>Auto-scheduled via WhatsApp AI: "Yes sure" (In-Person)</v>
       </c>
       <c r="K46" t="str">
-        <v>Pradhyumn_Kuril_Resume_(1)[1].docx</v>
+        <v>Work From Home</v>
       </c>
       <c r="L46" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M46" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N46" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O46" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T46" t="str">
         <v>16-Sept-2026, 12:54 am</v>
       </c>
-      <c r="P46" t="str">
+      <c r="U46" t="str">
         <v>ok</v>
       </c>
-      <c r="Q46" t="str">
+      <c r="V46" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Yes sure" (In-Person)</v>
       </c>
     </row>
@@ -2999,49 +3634,66 @@
         <v>Graphic Designer</v>
       </c>
       <c r="E47" t="str">
-        <v>Full-Time</v>
+        <v>I am graphic designer and video editor</v>
       </c>
       <c r="F47" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G47" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>25-Sept-2026, 11:00 am</v>
       </c>
       <c r="I47" t="str">
-        <v>Resume Received</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="J47" t="str">
-        <v>Not Scheduled</v>
+        <v>Auto-scheduled via WhatsApp AI: "Okay" (Online Google Meet)</v>
       </c>
       <c r="K47" t="str">
-        <v/>
+        <v>Work From Home</v>
       </c>
       <c r="L47" t="str">
-        <v>Indore</v>
+        <v>Online (Google Meet)</v>
       </c>
       <c r="M47" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N47" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O47" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R47" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S47" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T47" t="str">
         <v>16-Sept-2026, 1:58 am</v>
       </c>
-      <c r="P47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Zainab Ansari! 😊
-Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
-👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
-Please confirm (Yes / No or share your preferred time). 👍</v>
-      </c>
-      <c r="Q47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
+      <c r="U47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Zainab Ansari! 🔔 *Interview Reminder*
+Your *Online Google Meet Interview* for *Graphic Designer* at *Brand Setu Digital* is scheduled today at *Fri, 25 Sept, 11:00 am*. 💻
+📌 *Joining Link:* You will receive the Google Meet link here on WhatsApp 15 minutes before the interview starts.
+👉 Are you ready and available for the interview? Please confirm. 👍
+📞 Help: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V47" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Okay" (Online Google Meet)</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3055,45 +3707,57 @@
         <v>General Applicant</v>
       </c>
       <c r="E48" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I48" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J48" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L48" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M48" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N48" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O48" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R48" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S48" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T48" t="str">
         <v>16-Sept-2026, 2:27 am</v>
       </c>
-      <c r="P48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello Somya Jain! 👋
-Thank you for your interest in joining *BrandSetu Digital* for the *General Applicant* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
-👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
-- HR Team, BrandSetu Digital (+91 9329232025)</v>
-      </c>
-      <c r="Q48" t="str">
+      <c r="U48" t="str">
+        <v>Hello Somya Jain! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V48" t="str">
         <v/>
       </c>
     </row>
@@ -3111,42 +3775,57 @@
         <v>General Applicant</v>
       </c>
       <c r="E49" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G49" t="str">
-        <v>YES</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I49" t="str">
         <v>Resume Received</v>
       </c>
       <c r="J49" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>Full-Time</v>
       </c>
       <c r="L49" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M49" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N49" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O49" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R49" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S49" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T49" t="str">
         <v>16-Sept-2026, 3:58 am</v>
       </c>
-      <c r="P49" t="str">
-        <v>Dear Khushi Dixit! 🎉 Your in-person interview for the *General Applicant* position is confirmed at our Indore office (103 Orange Business Park, Bhawarkua). Best of luck! 👍</v>
-      </c>
-      <c r="Q49" t="str">
+      <c r="U49" t="str">
+        <v>Hello Khushi Dixit! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V49" t="str">
         <v/>
       </c>
     </row>
@@ -3164,45 +3843,60 @@
         <v>Influencer Collaboration</v>
       </c>
       <c r="E50" t="str">
-        <v>Influencer Collaboration</v>
+        <v>Preferred: Influencer Collaboration</v>
       </c>
       <c r="F50" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I50" t="str">
         <v>Resume Pending</v>
       </c>
       <c r="J50" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>Preferred: Influencer Collaboration</v>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="L50" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M50" t="str">
-        <v>YES</v>
+        <v/>
       </c>
       <c r="N50" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O50" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R50" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S50" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T50" t="str">
         <v>16-Sept-2026, 9:34 am</v>
       </c>
-      <c r="P50" t="str" xml:space="preserve">
+      <c r="U50" t="str" xml:space="preserve">
         <v xml:space="preserve">Dear Anjali! 👋
 Thank you for your interest in joining *BrandSetu Digital* for the *Influencer Collaboration* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
 👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
 - HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
       </c>
-      <c r="Q50" t="str">
+      <c r="V50" t="str">
         <v/>
       </c>
     </row>
@@ -3211,66 +3905,73 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Rahul</v>
+        <v>Rahul Dangi</v>
       </c>
       <c r="C51" t="str">
         <v>+919753928315</v>
       </c>
       <c r="D51" t="str">
-        <v>General Applicant</v>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="E51" t="str">
-        <v>Full-Time</v>
+        <v>Influencer Profile</v>
       </c>
       <c r="F51" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I51" t="str">
-        <v>Applied</v>
+        <v>Resume Received</v>
       </c>
       <c r="J51" t="str">
-        <v>Not Scheduled</v>
+        <v/>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>Influencer Collaboration</v>
       </c>
       <c r="L51" t="str">
-        <v>Indore</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="M51" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="N51" t="str">
-        <v>NO</v>
+        <v/>
       </c>
       <c r="O51" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R51" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T51" t="str">
         <v>16-Sept-2026, 10:40 am</v>
       </c>
-      <c r="P51" t="str" xml:space="preserve">
-        <v xml:space="preserve">Welcome to Brand Setu Digital! 🎉
-We are actively onboarding for these positions and collaborations:
-1️⃣ 🎬 *Video Editor*
-2️⃣ 🤖 *AI Video Expert*
-3️⃣ 🎨 *Graphic Designer*
-4️⃣ 🔎 *SEO &amp; AEO Expert*
-5️⃣ 📱 *Social Media Manager*
-6️⃣ 📢 *Digital Marketing Manager*
-7️⃣ ✨ *Influencer Collaboration!*
-💼 *Note:* If you are applying for any other *Digital Marketing Role* (SEO, SMM, Lead Gen, Content Writer, Web Developer, Telecaller, etc.), you can also reply with your role name.
-🌐 *Work Modes:* Full-Time (In-Office) | Work From Home (WFH) | Freelancer | Part-Time
-👉 Which **position or collaboration** would you like to apply for? (Please reply with number 1 to 7 or the name) 📝</v>
-      </c>
-      <c r="Q51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
+      <c r="U51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Rahul Dangi! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="V51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3284,46 +3985,64 @@
         <v>Social Media Manager</v>
       </c>
       <c r="E52" t="str">
+        <v>Full-Time (1 year of experience) [Work From Home]</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
         <v>Work From Home</v>
       </c>
-      <c r="F52" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="G52" t="str">
+      <c r="L52" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
         <v>PENDING</v>
       </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-      <c r="I52" t="str">
-        <v>Applied</v>
-      </c>
-      <c r="J52" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="K52" t="str">
-        <v>Full-Time (1 year of experience) [Work From Home]</v>
-      </c>
-      <c r="L52" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M52" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N52" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R52" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T52" t="str">
         <v>16-Sept-2026, 11:17 am</v>
       </c>
-      <c r="P52" t="str">
-        <v>Super! 📱 Please share your updated *Resume (PDF)* and your past managed social media profiles / growth proof here. 📄🚀</v>
-      </c>
-      <c r="Q52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
+      <c r="U52" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Poorva! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Social Media Manager* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3337,70 +4056,3129 @@
         <v>General Applicant</v>
       </c>
       <c r="E53" t="str">
-        <v>Full-Time</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v>In-Person (Indore Office)</v>
+        <v/>
       </c>
       <c r="G53" t="str">
-        <v>PENDING</v>
+        <v>Pending Visit</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="I53" t="str">
         <v>Campaign Sent</v>
       </c>
       <c r="J53" t="str">
+        <v>Outreach campaign broadcast sent</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L53" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R53" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S53" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T53" t="str">
+        <v>16-Sept-2026, 12:17 pm</v>
+      </c>
+      <c r="U53" t="str">
+        <v>Hello Candidate! 😊 Aapne BrandSetu Digital me job ke liye connect kiya tha. Kripya batayein aap inme se kis position ke liye apply karna chahte hain? (1. Video Editor, 2. AI Video Expert, 3. Graphic Designer, 4. SEO &amp; AEO Expert, 5. Social Media Manager, 6. Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V53" t="str">
+        <v>Outreach campaign broadcast sent</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Swaraj</v>
+      </c>
+      <c r="C54" t="str">
+        <v>+918269944132</v>
+      </c>
+      <c r="D54" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H54" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="K53" t="str">
-        <v/>
-      </c>
-      <c r="L53" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="M53" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N53" t="str">
-        <v>NO</v>
-      </c>
-      <c r="O53" t="str">
-        <v>16-Sept-2026, 12:17 pm</v>
-      </c>
-      <c r="P53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hello! 👋_x000d_
-_x000d_
-Brand Setu Digital is expanding its Creative &amp; Marketing Team! 🚀_x000d_
-_x000d_
-We are currently hiring for multiple positions:_x000d_
-_x000d_
-1️⃣ Video Editor – Reels / YouTube 🎬_x000d_
-2️⃣ AI Video Expert – AI Tools / Prompting 🤖_x000d_
-3️⃣ Graphic Designer – Photoshop / Figma 🎨_x000d_
-4️⃣ SEO &amp; AEO Expert 🔎_x000d_
-5️⃣ Social Media Manager 📱_x000d_
-6️⃣ Digital Marketing Manager 📢_x000d_
-7️⃣ Influencer Collaboration ✨_x000d_
-_x000d_
-💼 Full-Time | Work From Home | Freelance opportunities are available._x000d_
-_x000d_
-If you’re interested, please share your updated Resume (PDF) and mention which position you are applying for._x000d_
-_x000d_
-👉 Example: “I’m applying for Position 1 – Video Editor.”_x000d_
-_x000d_
-If you’re interested in multiple positions, you can mention all the positions you’d like to apply for._x000d_
-_x000d_
-Our HR team will review your profile and get back to you with the next steps. 😊</v>
-      </c>
-      <c r="Q53" t="str">
-        <v>Outreach campaign broadcast sent</v>
+      <c r="I54" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L54" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R54" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S54" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T54" t="str">
+        <v>18-Sept-2026, 11:25 am</v>
+      </c>
+      <c r="U54" t="str">
+        <v>Hello Swaraj! 😊 Aapne BrandSetu Digital me job ke liye connect kiya tha. Kripya batayein aap inme se kis position ke liye apply karna chahte hain? (1. Video Editor, 2. AI Video Expert, 3. Graphic Designer, 4. SEO &amp; AEO Expert, 5. Social Media Manager, 6. Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C55" t="str">
+        <v>+917312426395</v>
+      </c>
+      <c r="D55" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L55" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R55" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S55" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T55" t="str">
+        <v>19-Sept-2026, 1:12 am</v>
+      </c>
+      <c r="U55" t="str">
+        <v>Hello Candidate! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Ajay Dhanoliya</v>
+      </c>
+      <c r="C56" t="str">
+        <v>+916266581707</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R56" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S56" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T56" t="str">
+        <v>26-Sept-2026, 12:11 am</v>
+      </c>
+      <c r="U56" t="str">
+        <v>You are most welcome! We’ll be in touch with the Google Meet details shortly. Have a great day! 😊✨</v>
+      </c>
+      <c r="V56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Vickey Chouhan</v>
+      </c>
+      <c r="C57" t="str">
+        <v>+918103321559</v>
+      </c>
+      <c r="D57" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L57" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R57" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S57" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T57" t="str">
+        <v>26-Sept-2026, 12:20 am</v>
+      </c>
+      <c r="U57" t="str">
+        <v>Hello Vickey Chouhan! 😊 Regarding your application for *SEO &amp; AEO Expert* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Deeya Mandhana</v>
+      </c>
+      <c r="C58" t="str">
+        <v>+919425901960</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Work Mode: Freelancer</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H58" t="str">
+        <v>27-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "29th September - 2pm" (Online Google Meet)</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R58" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S58" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T58" t="str">
+        <v>26-Sept-2026, 12:36 am</v>
+      </c>
+      <c r="U58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Deeya Mandhana! 🔔 *Interview Reminder*
+Your *Online Google Meet Interview* for *Graphic Designer* at *Brand Setu Digital* is scheduled today at *Sun, 27 Sept, 11:00 am*. 💻
+📌 *Joining Link:* You will receive the Google Meet link here on WhatsApp 15 minutes before the interview starts.
+👉 Are you ready and available for the interview? Please confirm. 👍
+📞 Help: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V58" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "29th September - 2pm" (Online Google Meet)</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Mehak Hirwani</v>
+      </c>
+      <c r="C59" t="str">
+        <v>+919977353542</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Preferred: Freelancer</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R59" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S59" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T59" t="str">
+        <v>26-Sept-2026, 1:15 am</v>
+      </c>
+      <c r="U59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Mehak! Our team is currently reviewing your profile and will share the Google Meet link and time slot with you by today afternoon. 😊 
+Thank you for your patience! 👍✨</v>
+      </c>
+      <c r="V59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Vaishnavi Raghuwanshi</v>
+      </c>
+      <c r="C60" t="str">
+        <v>+919755633177</v>
+      </c>
+      <c r="D60" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L60" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R60" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S60" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T60" t="str">
+        <v>26-Sept-2026, 2:08 am</v>
+      </c>
+      <c r="U60" t="str">
+        <v>Hello Vaishnavi Raghuwanshi! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Palak Kumrawat</v>
+      </c>
+      <c r="C61" t="str">
+        <v>+919754353246</v>
+      </c>
+      <c r="D61" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L61" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R61" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S61" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T61" t="str">
+        <v>26-Sept-2026, 3:36 am</v>
+      </c>
+      <c r="U61" t="str">
+        <v>Hello Palak Kumrawat! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Rahul Done</v>
+      </c>
+      <c r="C62" t="str">
+        <v>+916268079461</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Experienced [Freelancer]</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H62" t="str">
+        <v>28-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (Online Google Meet)</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P62" t="str">
+        <v>https://www.figma.com/design/JFidyhnSVyDXhkkdXFs8Ua/my-protfoliyo?node-id=0-1&amp;p=f&amp;t=xJExgQwWsqpoPhXd-0</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R62" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S62" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T62" t="str">
+        <v>26-Sept-2026, 7:30 am</v>
+      </c>
+      <c r="U62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Rahul Done! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *11:00 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V62" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (Online Google Meet)</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Tushar Ray</v>
+      </c>
+      <c r="C63" t="str">
+        <v>+917725048771</v>
+      </c>
+      <c r="D63" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L63" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R63" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S63" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T63" t="str">
+        <v>26-Sept-2026, 9:11 am</v>
+      </c>
+      <c r="U63" t="str">
+        <v>Hello Tushar Ray! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Varsha</v>
+      </c>
+      <c r="C64" t="str">
+        <v>+918827608067</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Full-Time (1 year experience)</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H64" t="str">
+        <v>28-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Ma’am, by what time can I come for the interview today?" (In-Person)</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L64" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R64" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S64" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T64" t="str">
+        <v>26-Sept-2026, 9:44 am</v>
+      </c>
+      <c r="U64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Varsha! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *10:30 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V64" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Ma’am, by what time can I come for the interview today?" (In-Person)</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C65" t="str">
+        <v>+918103764331</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Full-Time (6 month) [Full-Time]</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H65" t="str">
+        <v>28-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "I will come today 11 am" (In-Person)</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L65" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R65" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S65" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T65" t="str">
+        <v>26-Sept-2026, 9:57 am</v>
+      </c>
+      <c r="U65" t="str">
+        <v>👍</v>
+      </c>
+      <c r="V65" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "I will come today 11 am" (In-Person)</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Raj</v>
+      </c>
+      <c r="C66" t="str">
+        <v>+917224994511</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Preferred: Influencer Collaboration</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>Influencer Collaboration</v>
+      </c>
+      <c r="L66" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R66" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S66" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T66" t="str">
+        <v>26-Sept-2026, 10:10 am</v>
+      </c>
+      <c r="U66" t="str">
+        <v>Dear Raj,Congratulations! You have been shortlisted for the interview at BrandSetu Digital.We are pleased to invite you for the next round of the selection process.📅 Date: 28/09/2026⏰ Time: 10:30 am                  📍Google Maps Location: https://maps.app.goo.gl/M6kv6SPc4rKMwj887?g_st=icBhawarkua main road orange business park floor 103 mc donald's building, IndorePlease make sure to reach on time.For any assistance, feel free to contact us.Looking forward to meeting you.Warm regards,BrandSetu Digital</v>
+      </c>
+      <c r="V66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C67" t="str">
+        <v>+917898450021</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Work Mode: Work From Home</v>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P67" t="str">
+        <v>https://www.behance.net/durvashipatidar2</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R67" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S67" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T67" t="str">
+        <v>26-Sept-2026, 11:50 am</v>
+      </c>
+      <c r="U67" t="str">
+        <v>Dear durvashi patidar,🎉 Your in-person interview for the *Graphic Designer* position is confirmed at our Indore office (103 Orange Business Park, Bhawarkua). Best of luck! 👍</v>
+      </c>
+      <c r="V67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Amisha</v>
+      </c>
+      <c r="C68" t="str">
+        <v>+918461043860</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Work Mode: Work From Home</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>Work From Home</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R68" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S68" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T68" t="str">
+        <v>26-Sept-2026, 11:53 am</v>
+      </c>
+      <c r="U68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Amisha! 👋
+Thank you for your interest in joining *BrandSetu Digital* for the *Graphic Designer* position. We noticed we haven't received your updated *Resume / Portfolio* yet. 📄
+👉 Please share your Resume (PDF) or Portfolio link here so we can proceed with scheduling your interview. 🚀
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Harsh Pareta</v>
+      </c>
+      <c r="C69" t="str">
+        <v>+916307204459</v>
+      </c>
+      <c r="D69" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R69" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S69" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T69" t="str">
+        <v>26-Sept-2026, 12:35 pm</v>
+      </c>
+      <c r="U69" t="str">
+        <v>Hello Harsh Pareta! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Pranav Patil</v>
+      </c>
+      <c r="C70" t="str">
+        <v>+919039209275</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E70" t="str">
+        <v>premiere pro</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H70" t="str">
+        <v>28-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "i I'll come at 11:00 o clock" (In-Person)</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L70" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R70" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S70" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T70" t="str">
+        <v>26-Sept-2026, 1:02 pm</v>
+      </c>
+      <c r="U70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Pranav Patil! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *11:00 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V70" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "i I'll come at 11:00 o clock" (In-Person)</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C71" t="str">
+        <v>+919644884324</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Full-Time (1Year experience years) [Full-Time]</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H71" t="str">
+        <v>27-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "No I will come 28/09/2026 time 11:00am" (In-Person)</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L71" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P71" t="str">
+        <v>https://drive.google.com/drive/folders/1GeowZEYueIZ6mlQiVlt68UMQZoiSm2De</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R71" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S71" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T71" t="str">
+        <v>26-Sept-2026, 1:03 pm</v>
+      </c>
+      <c r="U71" t="str">
+        <v>You can directly reach our HR team at **+91 9329232025** or</v>
+      </c>
+      <c r="V71" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "No I will come 28/09/2026 time 11:00am" (In-Person)</v>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Khushi Chouhan</v>
+      </c>
+      <c r="C72" t="str">
+        <v>+918602585853</v>
+      </c>
+      <c r="D72" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H72" t="str">
+        <v>28-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Ok I will confirm u tomorrow about the interview" (In-Person)</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L72" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R72" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S72" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T72" t="str">
+        <v>26-Sept-2026, 1:06 pm</v>
+      </c>
+      <c r="U72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Khushi Chouhan! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *11:00 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V72" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Ok I will confirm u tomorrow about the interview" (In-Person)</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C73" t="str">
+        <v>+919664472144</v>
+      </c>
+      <c r="D73" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L73" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R73" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S73" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T73" t="str">
+        <v>26-Sept-2026, 1:26 pm</v>
+      </c>
+      <c r="U73" t="str">
+        <v>Hello Candidate! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Vicky</v>
+      </c>
+      <c r="C74" t="str">
+        <v>+917225859454</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Experienced</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Online Requested</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Candidate requested online / virtual interview; pending HR Meet link</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v>28/09/2026 at 10:30 am</v>
+      </c>
+      <c r="O74" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R74" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S74" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T74" t="str">
+        <v>26-Sept-2026, 1:35 pm</v>
+      </c>
+      <c r="U74" t="str">
+        <v>Certainly! For Remote / Work From Home and Online (Virtual) interviews, our HR team will directly connect with you via WhatsApp / Call shortly to schedule and share the online meeting details. 🤝✨ Meanwhile, please ensure your updated Resume (PDF) and portfolio links are shared here. 👍</v>
+      </c>
+      <c r="V74" t="str">
+        <v>Candidate requested online / virtual interview; pending HR Meet link</v>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Harsh</v>
+      </c>
+      <c r="C75" t="str">
+        <v>+919399399365</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H75" t="str">
+        <v>27-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Tommorow is Sunday?" (In-Person)</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L75" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P75" t="str">
+        <v>Social: https://www.instagram.com/harshloggyy (N/A)</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R75" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S75" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T75" t="str">
+        <v>26-Sept-2026, 4:06 pm</v>
+      </c>
+      <c r="U75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Harsh! 🔔 *Interview Reminder*
+Your in-person interview for *Video Editor* at *Brand Setu Digital* is scheduled today at *Sun, 27 Sept, 10:30 am*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V75" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Tommorow is Sunday?" (In-Person)</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Soniya Kardam</v>
+      </c>
+      <c r="C76" t="str">
+        <v>+918889116217</v>
+      </c>
+      <c r="D76" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Preferred: Freelancer</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R76" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S76" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T76" t="str">
+        <v>26-Sept-2026, 4:39 pm</v>
+      </c>
+      <c r="U76" t="str">
+        <v>We have your details and our team is reviewing them. We will update you shortly! 👍</v>
+      </c>
+      <c r="V76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Sumit Jhalaya</v>
+      </c>
+      <c r="C77" t="str">
+        <v>+919329797483</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L77" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R77" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S77" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T77" t="str">
+        <v>26-Sept-2026, 4:51 pm</v>
+      </c>
+      <c r="U77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Sumit Jhalaya! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="V77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Priyansh Kala</v>
+      </c>
+      <c r="C78" t="str">
+        <v>+917415981143</v>
+      </c>
+      <c r="D78" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H78" t="str">
+        <v>28-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "No. I am available for the interview on Monday, 28th September between 10:00 AM to 12:00 PM" (In-Person)</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L78" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R78" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S78" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T78" t="str">
+        <v>26-Sept-2026, 6:46 pm</v>
+      </c>
+      <c r="U78" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Priyansh Kala! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *10:30 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V78" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "No. I am available for the interview on Monday, 28th September between 10:00 AM to 12:00 PM" (In-Person)</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Soumy Rai</v>
+      </c>
+      <c r="C79" t="str">
+        <v>+917415554789</v>
+      </c>
+      <c r="D79" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L79" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R79" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S79" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T79" t="str">
+        <v>26-Sept-2026, 7:29 pm</v>
+      </c>
+      <c r="U79" t="str">
+        <v>Hello Soumy Rai! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C80" t="str">
+        <v>+917869025453</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H80" t="str">
+        <v>28-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Sorry, I won’t be able to attend the interview today as I’m not feeling well. I apologize for the inconvenience. Could we please reschedule it?" (In-Person)</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L80" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R80" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S80" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T80" t="str">
+        <v>26-Sept-2026, 7:47 pm</v>
+      </c>
+      <c r="U80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Candidate! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *10:30 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V80" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Sorry, I won’t be able to attend the interview today as I’m not feeling well. I apologize for the inconvenience. Could we please reschedule it?" (In-Person)</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Sagar Kahar</v>
+      </c>
+      <c r="C81" t="str">
+        <v>+919993600859</v>
+      </c>
+      <c r="D81" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2  years</v>
+      </c>
+      <c r="F81" t="str">
+        <v>20000</v>
+      </c>
+      <c r="G81" t="str">
+        <v>28-Sept-2026, 3:50 pm</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Interview Attended</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Detailed Interview Feedback &amp; Description</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L81" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R81" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S81" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T81" t="str">
+        <v>26-Sept-2026, 8:49 pm</v>
+      </c>
+      <c r="U81" t="str">
+        <v>Hello Sagar Kahar! 😊 Regarding your application for *Video Editor* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V81" t="str">
+        <v>Detailed Interview Feedback &amp; Description</v>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Isha</v>
+      </c>
+      <c r="C82" t="str">
+        <v>+919691095750</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Other Digital Marketing Roles</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H82" t="str">
+        <v>29-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "Ma’am, I’m currently having a high fever and am not feeling well. I sincerely request you to kindly consider rescheduling my interview to day after tomorrow (Tuesday), if possible.
+I apologize for the inconvenience and would really appreciate your understanding and consideration. Thank you, Ma’am." (In-Person)</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L82" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R82" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S82" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T82" t="str">
+        <v>26-Sept-2026, 10:52 pm</v>
+      </c>
+      <c r="U82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Isha,
+Your interview at BrandSetu Digital has been rescheduled as requested.
+We are pleased to invite you for the next round of the selection process.
+📅 Date: 29/09/2026
+⏰ Time: 10:30 am
+📍Google Maps Location: https://maps.app.goo.gl/M6kv6SPc4rKMwj887?g_st=ic
+Bhawarkua main road orange business park floor 103 mc donald's building, Indore
+Please make sure to reach on time.
+For any assistance, feel free to contact us.
+Looking forward to meeting you.
+Warm regards,
+BrandSetu Digital</v>
+      </c>
+      <c r="V82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "Ma’am, I’m currently having a high fever and am not feeling well. I sincerely request you to kindly consider rescheduling my interview to day after tomorrow (Tuesday), if possible.
+I apologize for the inconvenience and would really appreciate your understanding and consideration. Thank you, Ma’am." (In-Person)</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Jai Shri Shyam</v>
+      </c>
+      <c r="C83" t="str">
+        <v>+919111990671</v>
+      </c>
+      <c r="D83" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L83" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R83" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S83" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T83" t="str">
+        <v>27-Sept-2026, 12:07 am</v>
+      </c>
+      <c r="U83" t="str">
+        <v>Hello Jai Shri Shyam! 😊 Regarding your application for *AI Video Expert* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>It Anshul</v>
+      </c>
+      <c r="C84" t="str">
+        <v>+919516902561</v>
+      </c>
+      <c r="D84" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L84" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R84" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S84" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T84" t="str">
+        <v>27-Sept-2026, 12:27 am</v>
+      </c>
+      <c r="U84" t="str">
+        <v>Hello It Anshul! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Ranu</v>
+      </c>
+      <c r="C85" t="str">
+        <v>+919893583620</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L85" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R85" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S85" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T85" t="str">
+        <v>27-Sept-2026, 3:19 am</v>
+      </c>
+      <c r="U85" t="str">
+        <v>Hello Ranu! 😊 Regarding your application for *Graphic Designer* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Mayur Resum</v>
+      </c>
+      <c r="C86" t="str">
+        <v>+918085330172</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Full-Time (3 year of experience)</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L86" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R86" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S86" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T86" t="str">
+        <v>27-Sept-2026, 8:39 am</v>
+      </c>
+      <c r="U86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Thank you for sharing your resume/portfolio! 📄✨
+Our HR team is currently reviewing your profile and work samples. We will connect with you shortly for the next steps! 👍</v>
+      </c>
+      <c r="V86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C87" t="str">
+        <v>+918827304710</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Experienced</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Online Requested</v>
+      </c>
+      <c r="J87" t="str">
+        <v>HR test note</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v>Mon, 28 Sept, 05:00 pm</v>
+      </c>
+      <c r="O87" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R87" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S87" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T87" t="str">
+        <v>27-Sept-2026, 9:36 am</v>
+      </c>
+      <c r="U87" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello! 🔔 *Interview Reminder*
+Your *Online Google Meet Interview* for *Graphic Designer* at *Brand Setu Digital* is scheduled today at *Mon, 28 Sept, 05:00 pm*. 💻
+📌 *Joining Link:* You will receive the Google Meet link here on WhatsApp 15 minutes before the interview starts.
+👉 Are you ready and available for the interview? Please confirm. 👍
+📞 Help: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V87" t="str">
+        <v>HR test note</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Jainul</v>
+      </c>
+      <c r="C88" t="str">
+        <v>+917869291064</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L88" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R88" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S88" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T88" t="str">
+        <v>27-Sept-2026, 10:07 am</v>
+      </c>
+      <c r="U88" t="str">
+        <v>Hello Jainul! 😊 Regarding your application for *Graphic Designer* at BrandSetu Digital: Could you please let us know if you are applying as a Fresher or Experienced? And what are your core tools/skills? 💼</v>
+      </c>
+      <c r="V88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89" xml:space="preserve">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Shirjal Verma</v>
+      </c>
+      <c r="C89" t="str">
+        <v>+919838804948</v>
+      </c>
+      <c r="D89" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E89" t="str">
+        <v>SHIRJAL VERMA Resume 1.pdf</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L89" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R89" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S89" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T89" t="str">
+        <v>27-Sept-2026, 12:57 pm</v>
+      </c>
+      <c r="U89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello Shirjal Verma! 😊
+Great news! Your profile and portfolio have been shortlisted by our HR team. 👏✨
+👉 Are you available to visit our Indore office (*103 Orange Business Park, Bhawarkua*) for an in-person practical interview tomorrow morning between *10:00 AM and 12:00 PM*? 🏢
+Please confirm (Yes / No or share your preferred time). 👍</v>
+      </c>
+      <c r="V89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Nilesh Parnam</v>
+      </c>
+      <c r="C90" t="str">
+        <v>+918120263254</v>
+      </c>
+      <c r="D90" t="str">
+        <v>AI Video Expert</v>
+      </c>
+      <c r="E90" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H90" t="str">
+        <v>28-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L90" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P90" t="str">
+        <v>https://www.behance.net/nileshparnam</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R90" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S90" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T90" t="str">
+        <v>27-Sept-2026, 1:13 pm</v>
+      </c>
+      <c r="U90" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Nilesh Parnam! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *10:30 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V90" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Deepak</v>
+      </c>
+      <c r="C91" t="str">
+        <v>+916261486716</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E91" t="str">
+        <v>[Image received]</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L91" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R91" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S91" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T91" t="str">
+        <v>27-Sept-2026, 1:18 pm</v>
+      </c>
+      <c r="U91" t="str" xml:space="preserve">
+        <v xml:space="preserve">No problem at all! Take your time. 😊 
+Whenever you are ready, just let us know your available time or preferred date for the interview, and we'll gladly coordinate for you. 👍</v>
+      </c>
+      <c r="V91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Arushii Chouhan</v>
+      </c>
+      <c r="C92" t="str">
+        <v>+919302997959</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Graphic Designer</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Experienced</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H92" t="str">
+        <v>28-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "okay thankyou" (Online Google Meet)</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Online (Google Meet)</v>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P92" t="str">
+        <v>https://www.behance.net/arushiichouhan25</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R92" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S92" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T92" t="str">
+        <v>27-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="U92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Arushii Chouhan! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *10:30 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V92" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "okay thankyou" (Online Google Meet)</v>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Shivani Yadav</v>
+      </c>
+      <c r="C93" t="str">
+        <v>+918602799857</v>
+      </c>
+      <c r="D93" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H93" t="str">
+        <v>28-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Can you schedule it for evening" (In-Person)</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L93" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R93" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S93" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T93" t="str">
+        <v>27-Sept-2026, 1:56 pm</v>
+      </c>
+      <c r="U93" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Shivani Yadav! 🔔 *Interview Reminder*
+Your in-person interview for *SEO &amp; AEO Expert* at *Brand Setu Digital* is scheduled today at *Mon, 28 Sept, 05:00 pm*.
+📍 *Office Address:*
+103 Orange Business Park, Bhawarkua Main Road, Near Apple Hospital, Indore (M.P.) - 452014
+👉 Are you on your way to our office for the interview? Please confirm. 👍
+📞 Help/Directions: +91 9329232025 / +91 9669765911
+- HR Team, Brand Setu Digital</v>
+      </c>
+      <c r="V93" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Can you schedule it for evening" (In-Person)</v>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Amit Singh</v>
+      </c>
+      <c r="C94" t="str">
+        <v>+917415321585</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Social Media Manager</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H94" t="str">
+        <v>28-Sept-2026, 10:30 am</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L94" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R94" t="str">
+        <v>NO</v>
+      </c>
+      <c r="S94" t="str">
+        <v>YES</v>
+      </c>
+      <c r="T94" t="str">
+        <v>27-Sept-2026, 2:32 pm</v>
+      </c>
+      <c r="U94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Amit Singh! 🔔
+Your in-person interview at *BrandSetu Digital* was scheduled today at *10:30 am*, but we noticed you were unable to visit our office.
+👉 Would you like to reschedule your interview for tomorrow or another date? Please let us know your preferred time so we can update your schedule. 👍
+- HR Team, BrandSetu Digital (+91 9329232025 / +91 9669765911)</v>
+      </c>
+      <c r="V94" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Frozen</v>
+      </c>
+      <c r="C95" t="str">
+        <v>+918889655875</v>
+      </c>
+      <c r="D95" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Resume Received</v>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L95" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v>YES</v>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R95" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S95" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T95" t="str">
+        <v>27-Sept-2026, 4:17 pm</v>
+      </c>
+      <c r="U95" t="str">
+        <v>Hello Frozen! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Mahak Lukkad</v>
+      </c>
+      <c r="C96" t="str">
+        <v>+917694818169</v>
+      </c>
+      <c r="D96" t="str">
+        <v>SEO &amp; AEO Expert</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Full-Time (6 month experience)</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L96" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R96" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S96" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T96" t="str">
+        <v>27-Sept-2026, 4:22 pm</v>
+      </c>
+      <c r="U96" t="str">
+        <v>You're welcome! See you at the interview. 👍</v>
+      </c>
+      <c r="V96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Shivam Rana</v>
+      </c>
+      <c r="C97" t="str">
+        <v>+917067847388</v>
+      </c>
+      <c r="D97" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v>Pending Visit</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>Full-Time</v>
+      </c>
+      <c r="L97" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R97" t="str">
+        <v>YES</v>
+      </c>
+      <c r="S97" t="str">
+        <v>NO</v>
+      </c>
+      <c r="T97" t="str">
+        <v>27-Sept-2026, 4:23 pm</v>
+      </c>
+      <c r="U97" t="str">
+        <v>Hello Shivam Rana! 😊 We noticed you connected with BrandSetu Digital regarding open positions. Could you please let us know which position or collaboration you would like to apply for? (Video Editor, AI Video Expert, Graphic Designer, SEO &amp; AEO Expert, Social Media Manager, Digital Marketing Manager) 📝</v>
+      </c>
+      <c r="V97" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V97"/>
   </ignoredErrors>
 </worksheet>
 </file>